--- a/SC26/artifacts/MCB/MCB.xlsx
+++ b/SC26/artifacts/MCB/MCB.xlsx
@@ -587,72 +587,72 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>TLB_BAT</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>IMU</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>BRUSA</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>BMS_LV</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>DSPACE</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>STEERING</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SCANNER</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>DATALOGGER</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>SB_FRONT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>SB_REAR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>TLB_BAT</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>STEERING</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>DSPACE</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>DIAG_TOOL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>SCANNER</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>BRUSA</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>DATALOGGER</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>EXTRA_NODE</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>IMU</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>BMS_LV</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>TPMS</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
@@ -728,17 +728,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
           <t>s</t>
@@ -757,13 +753,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
@@ -830,17 +830,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R3" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -859,13 +855,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X3" s="7" t="inlineStr"/>
-      <c r="Y3" s="6" t="inlineStr"/>
-      <c r="Z3" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr"/>
       <c r="AA3" s="6" t="inlineStr"/>
       <c r="AB3" s="6" t="inlineStr"/>
       <c r="AC3" s="6" t="inlineStr">
@@ -932,17 +932,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -961,13 +957,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X4" s="7" t="inlineStr"/>
-      <c r="Y4" s="6" t="inlineStr"/>
-      <c r="Z4" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr"/>
       <c r="AA4" s="6" t="inlineStr"/>
       <c r="AB4" s="6" t="inlineStr"/>
       <c r="AC4" s="6" t="inlineStr">
@@ -1034,17 +1034,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -1063,13 +1059,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X5" s="7" t="inlineStr"/>
-      <c r="Y5" s="6" t="inlineStr"/>
-      <c r="Z5" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y5" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr"/>
       <c r="AA5" s="6" t="inlineStr"/>
       <c r="AB5" s="6" t="inlineStr"/>
       <c r="AC5" s="6" t="inlineStr">
@@ -1140,17 +1140,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -1169,13 +1165,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr"/>
-      <c r="Y6" s="6" t="inlineStr"/>
-      <c r="Z6" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr"/>
       <c r="AA6" s="6" t="inlineStr"/>
       <c r="AB6" s="6" t="inlineStr"/>
       <c r="AC6" s="6" t="inlineStr">
@@ -1246,17 +1246,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -1275,13 +1271,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr"/>
-      <c r="Y7" s="6" t="inlineStr"/>
-      <c r="Z7" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr"/>
       <c r="AA7" s="6" t="inlineStr"/>
       <c r="AB7" s="6" t="inlineStr"/>
       <c r="AC7" s="6" t="inlineStr">
@@ -1352,17 +1352,13 @@
           <t>r</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
           <t>s</t>
@@ -1381,13 +1377,17 @@
           <t>r</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr"/>
-      <c r="Y8" s="6" t="inlineStr"/>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr"/>
       <c r="AA8" s="6" t="inlineStr"/>
       <c r="AB8" s="6" t="inlineStr"/>
       <c r="AC8" s="6" t="inlineStr">
@@ -1453,13 +1453,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr">
         <is>
@@ -1535,13 +1535,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P10" s="7" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O12" s="6" t="inlineStr"/>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P12" s="7" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr">
         <is>
@@ -1781,13 +1781,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P14" s="7" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr">
         <is>
@@ -2027,13 +2027,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P16" s="7" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="7" t="inlineStr">
         <is>
@@ -2109,13 +2109,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="7" t="inlineStr">
         <is>
@@ -2273,13 +2273,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O19" s="6" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P19" s="7" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O20" s="6" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P20" s="7" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
       <c r="R20" s="7" t="inlineStr">
         <is>
@@ -2437,13 +2437,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr">
         <is>
@@ -2519,13 +2519,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P22" s="7" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="7" t="inlineStr">
         <is>
@@ -2601,13 +2601,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P23" s="7" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr">
         <is>
@@ -2683,11 +2683,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2705,7 +2701,11 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr"/>
       <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="3" t="inlineStr"/>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
@@ -2773,11 +2773,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N25" s="7" t="inlineStr"/>
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
@@ -2795,7 +2791,11 @@
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="7" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="7" t="inlineStr"/>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y25" s="6" t="inlineStr"/>
       <c r="Z25" s="7" t="inlineStr"/>
       <c r="AA25" s="6" t="inlineStr"/>
@@ -2863,11 +2863,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
@@ -2885,7 +2881,11 @@
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="7" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="7" t="inlineStr"/>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y26" s="6" t="inlineStr"/>
       <c r="Z26" s="7" t="inlineStr"/>
       <c r="AA26" s="6" t="inlineStr"/>
@@ -2953,11 +2953,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N27" s="7" t="inlineStr"/>
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
@@ -2975,7 +2971,11 @@
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="7" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="7" t="inlineStr"/>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y27" s="6" t="inlineStr"/>
       <c r="Z27" s="7" t="inlineStr"/>
       <c r="AA27" s="6" t="inlineStr"/>
@@ -3043,11 +3043,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -3065,7 +3061,11 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr"/>
       <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+      <c r="X28" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="2" t="inlineStr"/>
@@ -3133,11 +3133,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N29" s="7" t="inlineStr"/>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
@@ -3155,7 +3151,11 @@
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="7" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="7" t="inlineStr"/>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y29" s="6" t="inlineStr"/>
       <c r="Z29" s="7" t="inlineStr"/>
       <c r="AA29" s="6" t="inlineStr"/>
@@ -3224,11 +3224,7 @@
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
-      <c r="O30" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="3" t="inlineStr">
@@ -3246,7 +3242,11 @@
       <c r="V30" s="3" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Y30" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
@@ -3314,11 +3314,7 @@
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="7" t="inlineStr">
@@ -3336,7 +3332,11 @@
       <c r="V31" s="7" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
       <c r="X31" s="7" t="inlineStr"/>
-      <c r="Y31" s="6" t="inlineStr"/>
+      <c r="Y31" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z31" s="7" t="inlineStr"/>
       <c r="AA31" s="6" t="inlineStr"/>
       <c r="AB31" s="6" t="inlineStr"/>
@@ -3404,11 +3404,7 @@
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="7" t="inlineStr">
@@ -3426,7 +3422,11 @@
       <c r="V32" s="7" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
       <c r="X32" s="7" t="inlineStr"/>
-      <c r="Y32" s="6" t="inlineStr"/>
+      <c r="Y32" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z32" s="7" t="inlineStr"/>
       <c r="AA32" s="6" t="inlineStr"/>
       <c r="AB32" s="6" t="inlineStr"/>
@@ -3494,11 +3494,7 @@
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="3" t="inlineStr">
@@ -3516,7 +3512,11 @@
       <c r="V33" s="3" t="inlineStr"/>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="3" t="inlineStr"/>
-      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Y33" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="inlineStr"/>
@@ -3576,11 +3576,7 @@
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="7" t="inlineStr">
@@ -3598,7 +3594,11 @@
       <c r="V34" s="7" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr"/>
-      <c r="Y34" s="6" t="inlineStr"/>
+      <c r="Y34" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z34" s="7" t="inlineStr"/>
       <c r="AA34" s="6" t="inlineStr"/>
       <c r="AB34" s="6" t="inlineStr"/>
@@ -3658,11 +3658,7 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="3" t="inlineStr">
@@ -3680,7 +3676,11 @@
       <c r="V35" s="3" t="inlineStr"/>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="3" t="inlineStr"/>
-      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Y35" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="inlineStr"/>
@@ -4246,7 +4246,11 @@
       <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="Q42" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -4263,11 +4267,7 @@
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr"/>
-      <c r="Z42" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
@@ -4336,7 +4336,11 @@
       <c r="N43" s="7" t="inlineStr"/>
       <c r="O43" s="6" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr"/>
-      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -4353,11 +4357,7 @@
       <c r="W43" s="6" t="inlineStr"/>
       <c r="X43" s="7" t="inlineStr"/>
       <c r="Y43" s="6" t="inlineStr"/>
-      <c r="Z43" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z43" s="7" t="inlineStr"/>
       <c r="AA43" s="6" t="inlineStr"/>
       <c r="AB43" s="6" t="inlineStr"/>
       <c r="AC43" s="6" t="inlineStr">
@@ -4426,7 +4426,11 @@
       <c r="N44" s="7" t="inlineStr"/>
       <c r="O44" s="6" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr"/>
-      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -4443,11 +4447,7 @@
       <c r="W44" s="6" t="inlineStr"/>
       <c r="X44" s="7" t="inlineStr"/>
       <c r="Y44" s="6" t="inlineStr"/>
-      <c r="Z44" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z44" s="7" t="inlineStr"/>
       <c r="AA44" s="6" t="inlineStr"/>
       <c r="AB44" s="6" t="inlineStr"/>
       <c r="AC44" s="6" t="inlineStr">
@@ -4774,17 +4774,17 @@
       <c r="N48" s="3" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="3" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="S48" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -4860,17 +4860,17 @@
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="6" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
-      <c r="Q49" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S49" s="6" t="inlineStr"/>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -4946,17 +4946,17 @@
       <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="6" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
-      <c r="Q50" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S50" s="6" t="inlineStr"/>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5032,17 +5032,17 @@
       <c r="N51" s="7" t="inlineStr"/>
       <c r="O51" s="6" t="inlineStr"/>
       <c r="P51" s="7" t="inlineStr"/>
-      <c r="Q51" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S51" s="6" t="inlineStr"/>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5118,17 +5118,17 @@
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="6" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr"/>
-      <c r="Q52" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S52" s="6" t="inlineStr"/>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5204,17 +5204,17 @@
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="6" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr"/>
-      <c r="Q53" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S53" s="6" t="inlineStr"/>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5290,17 +5290,17 @@
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="6" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr"/>
-      <c r="Q54" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S54" s="6" t="inlineStr"/>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5376,17 +5376,17 @@
       <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="6" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr"/>
-      <c r="Q55" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S55" s="6" t="inlineStr"/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5462,17 +5462,17 @@
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="6" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr"/>
-      <c r="Q56" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S56" s="6" t="inlineStr"/>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5548,17 +5548,17 @@
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="6" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
-      <c r="Q57" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S57" s="6" t="inlineStr"/>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5638,17 +5638,17 @@
       <c r="N58" s="7" t="inlineStr"/>
       <c r="O58" s="6" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
-      <c r="Q58" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S58" s="6" t="inlineStr"/>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5728,17 +5728,17 @@
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="6" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr"/>
-      <c r="Q59" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="7" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="S59" s="6" t="inlineStr"/>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -5894,11 +5894,7 @@
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="4" t="inlineStr">
@@ -5920,7 +5916,11 @@
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr"/>
-      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Z61" s="3" t="inlineStr"/>
       <c r="AA61" s="2" t="inlineStr"/>
       <c r="AB61" s="2" t="inlineStr"/>
@@ -6148,11 +6148,7 @@
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr"/>
-      <c r="O64" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="O64" s="6" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
       <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr">
@@ -6174,7 +6170,11 @@
         </is>
       </c>
       <c r="X64" s="7" t="inlineStr"/>
-      <c r="Y64" s="6" t="inlineStr"/>
+      <c r="Y64" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Z64" s="7" t="inlineStr"/>
       <c r="AA64" s="6" t="inlineStr"/>
       <c r="AB64" s="6" t="inlineStr"/>
@@ -6242,11 +6242,7 @@
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr"/>
-      <c r="O65" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="O65" s="6" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr">
@@ -6268,7 +6264,11 @@
         </is>
       </c>
       <c r="X65" s="7" t="inlineStr"/>
-      <c r="Y65" s="6" t="inlineStr"/>
+      <c r="Y65" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Z65" s="7" t="inlineStr"/>
       <c r="AA65" s="6" t="inlineStr"/>
       <c r="AB65" s="6" t="inlineStr"/>
@@ -7058,22 +7058,22 @@
       <c r="N74" s="3" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="3" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R74" s="3" t="inlineStr"/>
-      <c r="S74" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S74" s="2" t="inlineStr"/>
       <c r="T74" s="3" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="3" t="inlineStr"/>
       <c r="W74" s="2" t="inlineStr"/>
       <c r="X74" s="3" t="inlineStr"/>
       <c r="Y74" s="2" t="inlineStr"/>
-      <c r="Z74" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr"/>
@@ -7142,11 +7142,7 @@
       <c r="P75" s="3" t="inlineStr"/>
       <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="3" t="inlineStr"/>
-      <c r="S75" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S75" s="2" t="inlineStr"/>
       <c r="T75" s="3" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="3" t="inlineStr"/>
@@ -7157,7 +7153,11 @@
       </c>
       <c r="X75" s="3" t="inlineStr"/>
       <c r="Y75" s="2" t="inlineStr"/>
-      <c r="Z75" s="3" t="inlineStr"/>
+      <c r="Z75" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AA75" s="2" t="inlineStr"/>
       <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
@@ -7220,26 +7220,26 @@
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="3" t="inlineStr"/>
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="3" t="inlineStr"/>
-      <c r="S76" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S76" s="2" t="inlineStr"/>
       <c r="T76" s="3" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="3" t="inlineStr"/>
       <c r="W76" s="2" t="inlineStr"/>
       <c r="X76" s="3" t="inlineStr"/>
-      <c r="Y76" s="2" t="inlineStr"/>
-      <c r="Z76" s="3" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AA76" s="2" t="inlineStr"/>
       <c r="AB76" s="2" t="inlineStr"/>
       <c r="AC76" s="2" t="inlineStr">
@@ -7301,27 +7301,27 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr"/>
       <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="3" t="inlineStr"/>
-      <c r="S77" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S77" s="2" t="inlineStr"/>
       <c r="T77" s="3" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="3" t="inlineStr"/>
       <c r="W77" s="2" t="inlineStr"/>
-      <c r="X77" s="3" t="inlineStr"/>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Y77" s="2" t="inlineStr"/>
-      <c r="Z77" s="3" t="inlineStr"/>
+      <c r="Z77" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AA77" s="2" t="inlineStr"/>
       <c r="AB77" s="2" t="inlineStr"/>
       <c r="AC77" s="2" t="inlineStr">
@@ -7388,11 +7388,7 @@
       <c r="P78" s="3" t="inlineStr"/>
       <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="3" t="inlineStr"/>
-      <c r="S78" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S78" s="2" t="inlineStr"/>
       <c r="T78" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -7403,7 +7399,11 @@
       <c r="W78" s="2" t="inlineStr"/>
       <c r="X78" s="3" t="inlineStr"/>
       <c r="Y78" s="2" t="inlineStr"/>
-      <c r="Z78" s="3" t="inlineStr"/>
+      <c r="Z78" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AA78" s="2" t="inlineStr"/>
       <c r="AB78" s="2" t="inlineStr"/>
       <c r="AC78" s="2" t="inlineStr">
@@ -7465,27 +7465,27 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="P79" s="3" t="inlineStr"/>
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="3" t="inlineStr"/>
-      <c r="S79" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="S79" s="2" t="inlineStr"/>
       <c r="T79" s="3" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="3" t="inlineStr"/>
       <c r="W79" s="2" t="inlineStr"/>
       <c r="X79" s="3" t="inlineStr"/>
       <c r="Y79" s="2" t="inlineStr"/>
-      <c r="Z79" s="3" t="inlineStr"/>
+      <c r="Z79" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AA79" s="2" t="inlineStr"/>
       <c r="AB79" s="2" t="inlineStr"/>
       <c r="AC79" s="2" t="inlineStr">
@@ -7547,13 +7547,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P80" s="3" t="inlineStr"/>
       <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="3" t="inlineStr">
         <is>
@@ -7629,13 +7629,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O81" s="6" t="inlineStr"/>
-      <c r="P81" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P81" s="7" t="inlineStr"/>
       <c r="Q81" s="6" t="inlineStr"/>
       <c r="R81" s="7" t="inlineStr">
         <is>
@@ -7711,13 +7711,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O82" s="6" t="inlineStr"/>
-      <c r="P82" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P82" s="7" t="inlineStr"/>
       <c r="Q82" s="6" t="inlineStr"/>
       <c r="R82" s="7" t="inlineStr">
         <is>
@@ -7793,13 +7793,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O83" s="6" t="inlineStr"/>
-      <c r="P83" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P83" s="7" t="inlineStr"/>
       <c r="Q83" s="6" t="inlineStr"/>
       <c r="R83" s="7" t="inlineStr">
         <is>
@@ -7875,13 +7875,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O84" s="6" t="inlineStr"/>
-      <c r="P84" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P84" s="7" t="inlineStr"/>
       <c r="Q84" s="6" t="inlineStr"/>
       <c r="R84" s="7" t="inlineStr">
         <is>
@@ -7965,13 +7965,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr"/>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O85" s="6" t="inlineStr"/>
-      <c r="P85" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P85" s="7" t="inlineStr"/>
       <c r="Q85" s="6" t="inlineStr"/>
       <c r="R85" s="7" t="inlineStr">
         <is>
@@ -8056,11 +8056,7 @@
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr"/>
-      <c r="O86" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="3" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="3" t="inlineStr">
@@ -8078,7 +8074,11 @@
       <c r="V86" s="3" t="inlineStr"/>
       <c r="W86" s="2" t="inlineStr"/>
       <c r="X86" s="3" t="inlineStr"/>
-      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Y86" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z86" s="3" t="inlineStr"/>
       <c r="AA86" s="2" t="inlineStr"/>
       <c r="AB86" s="2" t="inlineStr"/>
@@ -8138,11 +8138,7 @@
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr"/>
-      <c r="O87" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O87" s="6" t="inlineStr"/>
       <c r="P87" s="7" t="inlineStr"/>
       <c r="Q87" s="6" t="inlineStr"/>
       <c r="R87" s="7" t="inlineStr">
@@ -8160,7 +8156,11 @@
       <c r="V87" s="7" t="inlineStr"/>
       <c r="W87" s="6" t="inlineStr"/>
       <c r="X87" s="7" t="inlineStr"/>
-      <c r="Y87" s="6" t="inlineStr"/>
+      <c r="Y87" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z87" s="7" t="inlineStr"/>
       <c r="AA87" s="6" t="inlineStr"/>
       <c r="AB87" s="6" t="inlineStr"/>
@@ -8220,11 +8220,7 @@
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr"/>
-      <c r="O88" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O88" s="6" t="inlineStr"/>
       <c r="P88" s="7" t="inlineStr"/>
       <c r="Q88" s="6" t="inlineStr"/>
       <c r="R88" s="7" t="inlineStr">
@@ -8242,7 +8238,11 @@
       <c r="V88" s="7" t="inlineStr"/>
       <c r="W88" s="6" t="inlineStr"/>
       <c r="X88" s="7" t="inlineStr"/>
-      <c r="Y88" s="6" t="inlineStr"/>
+      <c r="Y88" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z88" s="7" t="inlineStr"/>
       <c r="AA88" s="6" t="inlineStr"/>
       <c r="AB88" s="6" t="inlineStr"/>
@@ -8302,11 +8302,7 @@
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr"/>
-      <c r="O89" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O89" s="6" t="inlineStr"/>
       <c r="P89" s="7" t="inlineStr"/>
       <c r="Q89" s="6" t="inlineStr"/>
       <c r="R89" s="7" t="inlineStr">
@@ -8324,7 +8320,11 @@
       <c r="V89" s="7" t="inlineStr"/>
       <c r="W89" s="6" t="inlineStr"/>
       <c r="X89" s="7" t="inlineStr"/>
-      <c r="Y89" s="6" t="inlineStr"/>
+      <c r="Y89" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z89" s="7" t="inlineStr"/>
       <c r="AA89" s="6" t="inlineStr"/>
       <c r="AB89" s="6" t="inlineStr"/>
@@ -8383,11 +8383,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N90" s="3" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="3" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -8405,7 +8401,11 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="3" t="inlineStr"/>
       <c r="W90" s="2" t="inlineStr"/>
-      <c r="X90" s="3" t="inlineStr"/>
+      <c r="X90" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="3" t="inlineStr"/>
       <c r="AA90" s="2" t="inlineStr"/>
@@ -8465,11 +8465,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N91" s="7" t="inlineStr"/>
       <c r="O91" s="6" t="inlineStr"/>
       <c r="P91" s="7" t="inlineStr"/>
       <c r="Q91" s="6" t="inlineStr"/>
@@ -8487,7 +8483,11 @@
       <c r="U91" s="6" t="inlineStr"/>
       <c r="V91" s="7" t="inlineStr"/>
       <c r="W91" s="6" t="inlineStr"/>
-      <c r="X91" s="7" t="inlineStr"/>
+      <c r="X91" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y91" s="6" t="inlineStr"/>
       <c r="Z91" s="7" t="inlineStr"/>
       <c r="AA91" s="6" t="inlineStr"/>
@@ -8547,11 +8547,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N92" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N92" s="7" t="inlineStr"/>
       <c r="O92" s="6" t="inlineStr"/>
       <c r="P92" s="7" t="inlineStr"/>
       <c r="Q92" s="6" t="inlineStr"/>
@@ -8569,7 +8565,11 @@
       <c r="U92" s="6" t="inlineStr"/>
       <c r="V92" s="7" t="inlineStr"/>
       <c r="W92" s="6" t="inlineStr"/>
-      <c r="X92" s="7" t="inlineStr"/>
+      <c r="X92" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y92" s="6" t="inlineStr"/>
       <c r="Z92" s="7" t="inlineStr"/>
       <c r="AA92" s="6" t="inlineStr"/>
@@ -8629,11 +8629,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N93" s="3" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="3" t="inlineStr"/>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -8651,7 +8647,11 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="3" t="inlineStr"/>
       <c r="W93" s="2" t="inlineStr"/>
-      <c r="X93" s="3" t="inlineStr"/>
+      <c r="X93" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y93" s="2" t="inlineStr"/>
       <c r="Z93" s="3" t="inlineStr"/>
       <c r="AA93" s="2" t="inlineStr"/>
@@ -8719,11 +8719,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N94" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N94" s="7" t="inlineStr"/>
       <c r="O94" s="6" t="inlineStr"/>
       <c r="P94" s="7" t="inlineStr"/>
       <c r="Q94" s="6" t="inlineStr"/>
@@ -8741,7 +8737,11 @@
       <c r="U94" s="6" t="inlineStr"/>
       <c r="V94" s="7" t="inlineStr"/>
       <c r="W94" s="6" t="inlineStr"/>
-      <c r="X94" s="7" t="inlineStr"/>
+      <c r="X94" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y94" s="6" t="inlineStr"/>
       <c r="Z94" s="7" t="inlineStr"/>
       <c r="AA94" s="6" t="inlineStr"/>
@@ -8810,11 +8810,7 @@
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="3" t="inlineStr"/>
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="3" t="inlineStr">
@@ -8832,7 +8828,11 @@
       <c r="V95" s="3" t="inlineStr"/>
       <c r="W95" s="2" t="inlineStr"/>
       <c r="X95" s="3" t="inlineStr"/>
-      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Y95" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z95" s="3" t="inlineStr"/>
       <c r="AA95" s="2" t="inlineStr"/>
       <c r="AB95" s="2" t="inlineStr"/>
@@ -8900,11 +8900,7 @@
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr"/>
-      <c r="O96" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O96" s="6" t="inlineStr"/>
       <c r="P96" s="7" t="inlineStr"/>
       <c r="Q96" s="6" t="inlineStr"/>
       <c r="R96" s="7" t="inlineStr">
@@ -8922,7 +8918,11 @@
       <c r="V96" s="7" t="inlineStr"/>
       <c r="W96" s="6" t="inlineStr"/>
       <c r="X96" s="7" t="inlineStr"/>
-      <c r="Y96" s="6" t="inlineStr"/>
+      <c r="Y96" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z96" s="7" t="inlineStr"/>
       <c r="AA96" s="6" t="inlineStr"/>
       <c r="AB96" s="6" t="inlineStr"/>
@@ -8986,7 +8986,11 @@
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P97" s="3" t="inlineStr"/>
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="3" t="inlineStr"/>
@@ -8996,11 +9000,7 @@
       <c r="V97" s="3" t="inlineStr"/>
       <c r="W97" s="2" t="inlineStr"/>
       <c r="X97" s="3" t="inlineStr"/>
-      <c r="Y97" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
       <c r="Z97" s="3" t="inlineStr"/>
       <c r="AA97" s="2" t="inlineStr"/>
       <c r="AB97" s="2" t="inlineStr"/>
@@ -9064,7 +9064,11 @@
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr"/>
-      <c r="O98" s="6" t="inlineStr"/>
+      <c r="O98" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P98" s="7" t="inlineStr"/>
       <c r="Q98" s="6" t="inlineStr"/>
       <c r="R98" s="7" t="inlineStr"/>
@@ -9074,11 +9078,7 @@
       <c r="V98" s="7" t="inlineStr"/>
       <c r="W98" s="6" t="inlineStr"/>
       <c r="X98" s="7" t="inlineStr"/>
-      <c r="Y98" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y98" s="6" t="inlineStr"/>
       <c r="Z98" s="7" t="inlineStr"/>
       <c r="AA98" s="6" t="inlineStr"/>
       <c r="AB98" s="6" t="inlineStr"/>
@@ -9142,7 +9142,11 @@
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr"/>
-      <c r="O99" s="6" t="inlineStr"/>
+      <c r="O99" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P99" s="7" t="inlineStr"/>
       <c r="Q99" s="6" t="inlineStr"/>
       <c r="R99" s="7" t="inlineStr"/>
@@ -9152,11 +9156,7 @@
       <c r="V99" s="7" t="inlineStr"/>
       <c r="W99" s="6" t="inlineStr"/>
       <c r="X99" s="7" t="inlineStr"/>
-      <c r="Y99" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y99" s="6" t="inlineStr"/>
       <c r="Z99" s="7" t="inlineStr"/>
       <c r="AA99" s="6" t="inlineStr"/>
       <c r="AB99" s="6" t="inlineStr"/>
@@ -9220,7 +9220,11 @@
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="O100" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P100" s="3" t="inlineStr"/>
       <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="3" t="inlineStr"/>
@@ -9230,11 +9234,7 @@
       <c r="V100" s="3" t="inlineStr"/>
       <c r="W100" s="2" t="inlineStr"/>
       <c r="X100" s="3" t="inlineStr"/>
-      <c r="Y100" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
       <c r="Z100" s="3" t="inlineStr"/>
       <c r="AA100" s="2" t="inlineStr"/>
       <c r="AB100" s="2" t="inlineStr"/>
@@ -9298,7 +9298,11 @@
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr"/>
-      <c r="O101" s="6" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P101" s="7" t="inlineStr"/>
       <c r="Q101" s="6" t="inlineStr"/>
       <c r="R101" s="7" t="inlineStr"/>
@@ -9308,11 +9312,7 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="6" t="inlineStr"/>
       <c r="X101" s="7" t="inlineStr"/>
-      <c r="Y101" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y101" s="6" t="inlineStr"/>
       <c r="Z101" s="7" t="inlineStr"/>
       <c r="AA101" s="6" t="inlineStr"/>
       <c r="AB101" s="6" t="inlineStr"/>
@@ -9376,7 +9376,11 @@
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr"/>
-      <c r="O102" s="6" t="inlineStr"/>
+      <c r="O102" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P102" s="7" t="inlineStr"/>
       <c r="Q102" s="6" t="inlineStr"/>
       <c r="R102" s="7" t="inlineStr"/>
@@ -9386,11 +9390,7 @@
       <c r="V102" s="7" t="inlineStr"/>
       <c r="W102" s="6" t="inlineStr"/>
       <c r="X102" s="7" t="inlineStr"/>
-      <c r="Y102" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y102" s="6" t="inlineStr"/>
       <c r="Z102" s="7" t="inlineStr"/>
       <c r="AA102" s="6" t="inlineStr"/>
       <c r="AB102" s="6" t="inlineStr"/>
@@ -9454,7 +9454,11 @@
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
+      <c r="O103" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P103" s="3" t="inlineStr"/>
       <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="3" t="inlineStr"/>
@@ -9464,11 +9468,7 @@
       <c r="V103" s="3" t="inlineStr"/>
       <c r="W103" s="2" t="inlineStr"/>
       <c r="X103" s="3" t="inlineStr"/>
-      <c r="Y103" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
       <c r="Z103" s="3" t="inlineStr"/>
       <c r="AA103" s="2" t="inlineStr"/>
       <c r="AB103" s="2" t="inlineStr"/>
@@ -9532,7 +9532,11 @@
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr"/>
-      <c r="O104" s="6" t="inlineStr"/>
+      <c r="O104" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P104" s="7" t="inlineStr"/>
       <c r="Q104" s="6" t="inlineStr"/>
       <c r="R104" s="7" t="inlineStr"/>
@@ -9542,11 +9546,7 @@
       <c r="V104" s="7" t="inlineStr"/>
       <c r="W104" s="6" t="inlineStr"/>
       <c r="X104" s="7" t="inlineStr"/>
-      <c r="Y104" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y104" s="6" t="inlineStr"/>
       <c r="Z104" s="7" t="inlineStr"/>
       <c r="AA104" s="6" t="inlineStr"/>
       <c r="AB104" s="6" t="inlineStr"/>
@@ -9610,7 +9610,11 @@
         </is>
       </c>
       <c r="N105" s="7" t="inlineStr"/>
-      <c r="O105" s="6" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P105" s="7" t="inlineStr"/>
       <c r="Q105" s="6" t="inlineStr"/>
       <c r="R105" s="7" t="inlineStr"/>
@@ -9620,11 +9624,7 @@
       <c r="V105" s="7" t="inlineStr"/>
       <c r="W105" s="6" t="inlineStr"/>
       <c r="X105" s="7" t="inlineStr"/>
-      <c r="Y105" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y105" s="6" t="inlineStr"/>
       <c r="Z105" s="7" t="inlineStr"/>
       <c r="AA105" s="6" t="inlineStr"/>
       <c r="AB105" s="6" t="inlineStr"/>
@@ -9688,7 +9688,11 @@
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
+      <c r="O106" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P106" s="3" t="inlineStr"/>
       <c r="Q106" s="2" t="inlineStr"/>
       <c r="R106" s="3" t="inlineStr"/>
@@ -9698,11 +9702,7 @@
       <c r="V106" s="3" t="inlineStr"/>
       <c r="W106" s="2" t="inlineStr"/>
       <c r="X106" s="3" t="inlineStr"/>
-      <c r="Y106" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
       <c r="Z106" s="3" t="inlineStr"/>
       <c r="AA106" s="2" t="inlineStr"/>
       <c r="AB106" s="2" t="inlineStr"/>
@@ -9766,7 +9766,11 @@
         </is>
       </c>
       <c r="N107" s="7" t="inlineStr"/>
-      <c r="O107" s="6" t="inlineStr"/>
+      <c r="O107" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P107" s="7" t="inlineStr"/>
       <c r="Q107" s="6" t="inlineStr"/>
       <c r="R107" s="7" t="inlineStr"/>
@@ -9776,11 +9780,7 @@
       <c r="V107" s="7" t="inlineStr"/>
       <c r="W107" s="6" t="inlineStr"/>
       <c r="X107" s="7" t="inlineStr"/>
-      <c r="Y107" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y107" s="6" t="inlineStr"/>
       <c r="Z107" s="7" t="inlineStr"/>
       <c r="AA107" s="6" t="inlineStr"/>
       <c r="AB107" s="6" t="inlineStr"/>
@@ -9844,7 +9844,11 @@
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
+      <c r="O108" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P108" s="3" t="inlineStr"/>
       <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="3" t="inlineStr"/>
@@ -9854,11 +9858,7 @@
       <c r="V108" s="3" t="inlineStr"/>
       <c r="W108" s="2" t="inlineStr"/>
       <c r="X108" s="3" t="inlineStr"/>
-      <c r="Y108" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
       <c r="Z108" s="3" t="inlineStr"/>
       <c r="AA108" s="2" t="inlineStr"/>
       <c r="AB108" s="2" t="inlineStr"/>
@@ -9922,7 +9922,11 @@
         </is>
       </c>
       <c r="N109" s="7" t="inlineStr"/>
-      <c r="O109" s="6" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P109" s="7" t="inlineStr"/>
       <c r="Q109" s="6" t="inlineStr"/>
       <c r="R109" s="7" t="inlineStr"/>
@@ -9932,11 +9936,7 @@
       <c r="V109" s="7" t="inlineStr"/>
       <c r="W109" s="6" t="inlineStr"/>
       <c r="X109" s="7" t="inlineStr"/>
-      <c r="Y109" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y109" s="6" t="inlineStr"/>
       <c r="Z109" s="7" t="inlineStr"/>
       <c r="AA109" s="6" t="inlineStr"/>
       <c r="AB109" s="6" t="inlineStr"/>
@@ -10000,7 +10000,11 @@
         </is>
       </c>
       <c r="N110" s="7" t="inlineStr"/>
-      <c r="O110" s="6" t="inlineStr"/>
+      <c r="O110" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P110" s="7" t="inlineStr"/>
       <c r="Q110" s="6" t="inlineStr"/>
       <c r="R110" s="7" t="inlineStr"/>
@@ -10010,11 +10014,7 @@
       <c r="V110" s="7" t="inlineStr"/>
       <c r="W110" s="6" t="inlineStr"/>
       <c r="X110" s="7" t="inlineStr"/>
-      <c r="Y110" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y110" s="6" t="inlineStr"/>
       <c r="Z110" s="7" t="inlineStr"/>
       <c r="AA110" s="6" t="inlineStr"/>
       <c r="AB110" s="6" t="inlineStr"/>
@@ -10078,7 +10078,11 @@
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
+      <c r="O111" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P111" s="3" t="inlineStr"/>
       <c r="Q111" s="2" t="inlineStr"/>
       <c r="R111" s="3" t="inlineStr"/>
@@ -10088,11 +10092,7 @@
       <c r="V111" s="3" t="inlineStr"/>
       <c r="W111" s="2" t="inlineStr"/>
       <c r="X111" s="3" t="inlineStr"/>
-      <c r="Y111" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
       <c r="Z111" s="3" t="inlineStr"/>
       <c r="AA111" s="2" t="inlineStr"/>
       <c r="AB111" s="2" t="inlineStr"/>
@@ -10156,7 +10156,11 @@
         </is>
       </c>
       <c r="N112" s="7" t="inlineStr"/>
-      <c r="O112" s="6" t="inlineStr"/>
+      <c r="O112" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P112" s="7" t="inlineStr"/>
       <c r="Q112" s="6" t="inlineStr"/>
       <c r="R112" s="7" t="inlineStr"/>
@@ -10166,11 +10170,7 @@
       <c r="V112" s="7" t="inlineStr"/>
       <c r="W112" s="6" t="inlineStr"/>
       <c r="X112" s="7" t="inlineStr"/>
-      <c r="Y112" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y112" s="6" t="inlineStr"/>
       <c r="Z112" s="7" t="inlineStr"/>
       <c r="AA112" s="6" t="inlineStr"/>
       <c r="AB112" s="6" t="inlineStr"/>
@@ -10234,7 +10234,11 @@
         </is>
       </c>
       <c r="N113" s="7" t="inlineStr"/>
-      <c r="O113" s="6" t="inlineStr"/>
+      <c r="O113" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P113" s="7" t="inlineStr"/>
       <c r="Q113" s="6" t="inlineStr"/>
       <c r="R113" s="7" t="inlineStr"/>
@@ -10244,11 +10248,7 @@
       <c r="V113" s="7" t="inlineStr"/>
       <c r="W113" s="6" t="inlineStr"/>
       <c r="X113" s="7" t="inlineStr"/>
-      <c r="Y113" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y113" s="6" t="inlineStr"/>
       <c r="Z113" s="7" t="inlineStr"/>
       <c r="AA113" s="6" t="inlineStr"/>
       <c r="AB113" s="6" t="inlineStr"/>
@@ -10312,7 +10312,11 @@
         </is>
       </c>
       <c r="N114" s="7" t="inlineStr"/>
-      <c r="O114" s="6" t="inlineStr"/>
+      <c r="O114" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="P114" s="7" t="inlineStr"/>
       <c r="Q114" s="6" t="inlineStr"/>
       <c r="R114" s="7" t="inlineStr"/>
@@ -10322,11 +10326,7 @@
       <c r="V114" s="7" t="inlineStr"/>
       <c r="W114" s="6" t="inlineStr"/>
       <c r="X114" s="7" t="inlineStr"/>
-      <c r="Y114" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Y114" s="6" t="inlineStr"/>
       <c r="Z114" s="7" t="inlineStr"/>
       <c r="AA114" s="6" t="inlineStr"/>
       <c r="AB114" s="6" t="inlineStr"/>
@@ -10389,27 +10389,27 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N115" s="3" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O115" s="2" t="inlineStr"/>
-      <c r="P115" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P115" s="3" t="inlineStr"/>
       <c r="Q115" s="2" t="inlineStr"/>
       <c r="R115" s="3" t="inlineStr"/>
-      <c r="S115" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S115" s="2" t="inlineStr"/>
       <c r="T115" s="3" t="inlineStr"/>
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="3" t="inlineStr"/>
       <c r="W115" s="2" t="inlineStr"/>
       <c r="X115" s="3" t="inlineStr"/>
       <c r="Y115" s="2" t="inlineStr"/>
-      <c r="Z115" s="3" t="inlineStr"/>
+      <c r="Z115" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA115" s="2" t="inlineStr"/>
       <c r="AB115" s="2" t="inlineStr"/>
       <c r="AC115" s="2" t="inlineStr">
@@ -10471,27 +10471,27 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="3" t="inlineStr"/>
       <c r="Q116" s="2" t="inlineStr"/>
       <c r="R116" s="3" t="inlineStr"/>
-      <c r="S116" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S116" s="2" t="inlineStr"/>
       <c r="T116" s="3" t="inlineStr"/>
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="3" t="inlineStr"/>
       <c r="W116" s="2" t="inlineStr"/>
-      <c r="X116" s="3" t="inlineStr"/>
+      <c r="X116" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y116" s="2" t="inlineStr"/>
-      <c r="Z116" s="3" t="inlineStr"/>
+      <c r="Z116" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA116" s="2" t="inlineStr"/>
       <c r="AB116" s="2" t="inlineStr"/>
       <c r="AC116" s="2" t="inlineStr">
@@ -10554,26 +10554,26 @@
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr"/>
-      <c r="O117" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O117" s="2" t="inlineStr"/>
       <c r="P117" s="3" t="inlineStr"/>
       <c r="Q117" s="2" t="inlineStr"/>
       <c r="R117" s="3" t="inlineStr"/>
-      <c r="S117" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S117" s="2" t="inlineStr"/>
       <c r="T117" s="3" t="inlineStr"/>
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="3" t="inlineStr"/>
       <c r="W117" s="2" t="inlineStr"/>
       <c r="X117" s="3" t="inlineStr"/>
-      <c r="Y117" s="2" t="inlineStr"/>
-      <c r="Z117" s="3" t="inlineStr"/>
+      <c r="Y117" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="Z117" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA117" s="2" t="inlineStr"/>
       <c r="AB117" s="2" t="inlineStr"/>
       <c r="AC117" s="2" t="inlineStr">
@@ -10638,22 +10638,22 @@
       <c r="N118" s="3" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="3" t="inlineStr"/>
-      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="Q118" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R118" s="3" t="inlineStr"/>
-      <c r="S118" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S118" s="2" t="inlineStr"/>
       <c r="T118" s="3" t="inlineStr"/>
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="3" t="inlineStr"/>
       <c r="W118" s="2" t="inlineStr"/>
       <c r="X118" s="3" t="inlineStr"/>
       <c r="Y118" s="2" t="inlineStr"/>
-      <c r="Z118" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
+      <c r="Z118" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
         </is>
       </c>
       <c r="AA118" s="2" t="inlineStr"/>
@@ -10722,11 +10722,7 @@
       <c r="P119" s="3" t="inlineStr"/>
       <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="3" t="inlineStr"/>
-      <c r="S119" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S119" s="2" t="inlineStr"/>
       <c r="T119" s="3" t="inlineStr"/>
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="3" t="inlineStr"/>
@@ -10737,7 +10733,11 @@
       </c>
       <c r="X119" s="3" t="inlineStr"/>
       <c r="Y119" s="2" t="inlineStr"/>
-      <c r="Z119" s="3" t="inlineStr"/>
+      <c r="Z119" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA119" s="2" t="inlineStr"/>
       <c r="AB119" s="2" t="inlineStr"/>
       <c r="AC119" s="2" t="inlineStr">
@@ -10808,18 +10808,18 @@
           <t>s</t>
         </is>
       </c>
-      <c r="S120" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S120" s="2" t="inlineStr"/>
       <c r="T120" s="3" t="inlineStr"/>
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="3" t="inlineStr"/>
       <c r="W120" s="2" t="inlineStr"/>
       <c r="X120" s="3" t="inlineStr"/>
       <c r="Y120" s="2" t="inlineStr"/>
-      <c r="Z120" s="3" t="inlineStr"/>
+      <c r="Z120" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA120" s="2" t="inlineStr"/>
       <c r="AB120" s="2" t="inlineStr"/>
       <c r="AC120" s="2" t="inlineStr">
@@ -10886,11 +10886,7 @@
       <c r="P121" s="3" t="inlineStr"/>
       <c r="Q121" s="2" t="inlineStr"/>
       <c r="R121" s="3" t="inlineStr"/>
-      <c r="S121" s="2" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="S121" s="2" t="inlineStr"/>
       <c r="T121" s="4" t="inlineStr">
         <is>
           <t>s</t>
@@ -10901,7 +10897,11 @@
       <c r="W121" s="2" t="inlineStr"/>
       <c r="X121" s="3" t="inlineStr"/>
       <c r="Y121" s="2" t="inlineStr"/>
-      <c r="Z121" s="3" t="inlineStr"/>
+      <c r="Z121" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="AA121" s="2" t="inlineStr"/>
       <c r="AB121" s="2" t="inlineStr"/>
       <c r="AC121" s="2" t="inlineStr">
@@ -14308,7 +14308,11 @@
       <c r="N160" s="3" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr"/>
       <c r="P160" s="3" t="inlineStr"/>
-      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="Q160" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R160" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -14325,11 +14329,7 @@
       <c r="W160" s="2" t="inlineStr"/>
       <c r="X160" s="3" t="inlineStr"/>
       <c r="Y160" s="2" t="inlineStr"/>
-      <c r="Z160" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z160" s="3" t="inlineStr"/>
       <c r="AA160" s="2" t="inlineStr"/>
       <c r="AB160" s="2" t="inlineStr"/>
       <c r="AC160" s="2" t="inlineStr"/>
@@ -14390,7 +14390,11 @@
       <c r="N161" s="7" t="inlineStr"/>
       <c r="O161" s="6" t="inlineStr"/>
       <c r="P161" s="7" t="inlineStr"/>
-      <c r="Q161" s="6" t="inlineStr"/>
+      <c r="Q161" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14407,11 +14411,7 @@
       <c r="W161" s="6" t="inlineStr"/>
       <c r="X161" s="7" t="inlineStr"/>
       <c r="Y161" s="6" t="inlineStr"/>
-      <c r="Z161" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z161" s="7" t="inlineStr"/>
       <c r="AA161" s="6" t="inlineStr"/>
       <c r="AB161" s="6" t="inlineStr"/>
       <c r="AC161" s="6" t="inlineStr"/>
@@ -14472,7 +14472,11 @@
       <c r="N162" s="7" t="inlineStr"/>
       <c r="O162" s="6" t="inlineStr"/>
       <c r="P162" s="7" t="inlineStr"/>
-      <c r="Q162" s="6" t="inlineStr"/>
+      <c r="Q162" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14489,11 +14493,7 @@
       <c r="W162" s="6" t="inlineStr"/>
       <c r="X162" s="7" t="inlineStr"/>
       <c r="Y162" s="6" t="inlineStr"/>
-      <c r="Z162" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z162" s="7" t="inlineStr"/>
       <c r="AA162" s="6" t="inlineStr"/>
       <c r="AB162" s="6" t="inlineStr"/>
       <c r="AC162" s="6" t="inlineStr"/>
@@ -14554,7 +14554,11 @@
       <c r="N163" s="7" t="inlineStr"/>
       <c r="O163" s="6" t="inlineStr"/>
       <c r="P163" s="7" t="inlineStr"/>
-      <c r="Q163" s="6" t="inlineStr"/>
+      <c r="Q163" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14571,11 +14575,7 @@
       <c r="W163" s="6" t="inlineStr"/>
       <c r="X163" s="7" t="inlineStr"/>
       <c r="Y163" s="6" t="inlineStr"/>
-      <c r="Z163" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z163" s="7" t="inlineStr"/>
       <c r="AA163" s="6" t="inlineStr"/>
       <c r="AB163" s="6" t="inlineStr"/>
       <c r="AC163" s="6" t="inlineStr"/>
@@ -14636,7 +14636,11 @@
       <c r="N164" s="7" t="inlineStr"/>
       <c r="O164" s="6" t="inlineStr"/>
       <c r="P164" s="7" t="inlineStr"/>
-      <c r="Q164" s="6" t="inlineStr"/>
+      <c r="Q164" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14653,11 +14657,7 @@
       <c r="W164" s="6" t="inlineStr"/>
       <c r="X164" s="7" t="inlineStr"/>
       <c r="Y164" s="6" t="inlineStr"/>
-      <c r="Z164" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z164" s="7" t="inlineStr"/>
       <c r="AA164" s="6" t="inlineStr"/>
       <c r="AB164" s="6" t="inlineStr"/>
       <c r="AC164" s="6" t="inlineStr"/>
@@ -14718,7 +14718,11 @@
       <c r="N165" s="7" t="inlineStr"/>
       <c r="O165" s="6" t="inlineStr"/>
       <c r="P165" s="7" t="inlineStr"/>
-      <c r="Q165" s="6" t="inlineStr"/>
+      <c r="Q165" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14735,11 +14739,7 @@
       <c r="W165" s="6" t="inlineStr"/>
       <c r="X165" s="7" t="inlineStr"/>
       <c r="Y165" s="6" t="inlineStr"/>
-      <c r="Z165" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z165" s="7" t="inlineStr"/>
       <c r="AA165" s="6" t="inlineStr"/>
       <c r="AB165" s="6" t="inlineStr"/>
       <c r="AC165" s="6" t="inlineStr"/>
@@ -14800,7 +14800,11 @@
       <c r="N166" s="7" t="inlineStr"/>
       <c r="O166" s="6" t="inlineStr"/>
       <c r="P166" s="7" t="inlineStr"/>
-      <c r="Q166" s="6" t="inlineStr"/>
+      <c r="Q166" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14817,11 +14821,7 @@
       <c r="W166" s="6" t="inlineStr"/>
       <c r="X166" s="7" t="inlineStr"/>
       <c r="Y166" s="6" t="inlineStr"/>
-      <c r="Z166" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z166" s="7" t="inlineStr"/>
       <c r="AA166" s="6" t="inlineStr"/>
       <c r="AB166" s="6" t="inlineStr"/>
       <c r="AC166" s="6" t="inlineStr"/>
@@ -14882,7 +14882,11 @@
       <c r="N167" s="7" t="inlineStr"/>
       <c r="O167" s="6" t="inlineStr"/>
       <c r="P167" s="7" t="inlineStr"/>
-      <c r="Q167" s="6" t="inlineStr"/>
+      <c r="Q167" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14899,11 +14903,7 @@
       <c r="W167" s="6" t="inlineStr"/>
       <c r="X167" s="7" t="inlineStr"/>
       <c r="Y167" s="6" t="inlineStr"/>
-      <c r="Z167" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z167" s="7" t="inlineStr"/>
       <c r="AA167" s="6" t="inlineStr"/>
       <c r="AB167" s="6" t="inlineStr"/>
       <c r="AC167" s="6" t="inlineStr"/>
@@ -14964,7 +14964,11 @@
       <c r="N168" s="7" t="inlineStr"/>
       <c r="O168" s="6" t="inlineStr"/>
       <c r="P168" s="7" t="inlineStr"/>
-      <c r="Q168" s="6" t="inlineStr"/>
+      <c r="Q168" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -14981,11 +14985,7 @@
       <c r="W168" s="6" t="inlineStr"/>
       <c r="X168" s="7" t="inlineStr"/>
       <c r="Y168" s="6" t="inlineStr"/>
-      <c r="Z168" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z168" s="7" t="inlineStr"/>
       <c r="AA168" s="6" t="inlineStr"/>
       <c r="AB168" s="6" t="inlineStr"/>
       <c r="AC168" s="6" t="inlineStr"/>
@@ -15046,7 +15046,11 @@
       <c r="N169" s="7" t="inlineStr"/>
       <c r="O169" s="6" t="inlineStr"/>
       <c r="P169" s="7" t="inlineStr"/>
-      <c r="Q169" s="6" t="inlineStr"/>
+      <c r="Q169" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R169" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15063,11 +15067,7 @@
       <c r="W169" s="6" t="inlineStr"/>
       <c r="X169" s="7" t="inlineStr"/>
       <c r="Y169" s="6" t="inlineStr"/>
-      <c r="Z169" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z169" s="7" t="inlineStr"/>
       <c r="AA169" s="6" t="inlineStr"/>
       <c r="AB169" s="6" t="inlineStr"/>
       <c r="AC169" s="6" t="inlineStr"/>
@@ -15128,7 +15128,11 @@
       <c r="N170" s="7" t="inlineStr"/>
       <c r="O170" s="6" t="inlineStr"/>
       <c r="P170" s="7" t="inlineStr"/>
-      <c r="Q170" s="6" t="inlineStr"/>
+      <c r="Q170" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R170" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15145,11 +15149,7 @@
       <c r="W170" s="6" t="inlineStr"/>
       <c r="X170" s="7" t="inlineStr"/>
       <c r="Y170" s="6" t="inlineStr"/>
-      <c r="Z170" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z170" s="7" t="inlineStr"/>
       <c r="AA170" s="6" t="inlineStr"/>
       <c r="AB170" s="6" t="inlineStr"/>
       <c r="AC170" s="6" t="inlineStr"/>
@@ -15210,7 +15210,11 @@
       <c r="N171" s="7" t="inlineStr"/>
       <c r="O171" s="6" t="inlineStr"/>
       <c r="P171" s="7" t="inlineStr"/>
-      <c r="Q171" s="6" t="inlineStr"/>
+      <c r="Q171" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R171" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15227,11 +15231,7 @@
       <c r="W171" s="6" t="inlineStr"/>
       <c r="X171" s="7" t="inlineStr"/>
       <c r="Y171" s="6" t="inlineStr"/>
-      <c r="Z171" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z171" s="7" t="inlineStr"/>
       <c r="AA171" s="6" t="inlineStr"/>
       <c r="AB171" s="6" t="inlineStr"/>
       <c r="AC171" s="6" t="inlineStr"/>
@@ -15292,7 +15292,11 @@
       <c r="N172" s="7" t="inlineStr"/>
       <c r="O172" s="6" t="inlineStr"/>
       <c r="P172" s="7" t="inlineStr"/>
-      <c r="Q172" s="6" t="inlineStr"/>
+      <c r="Q172" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R172" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15309,11 +15313,7 @@
       <c r="W172" s="6" t="inlineStr"/>
       <c r="X172" s="7" t="inlineStr"/>
       <c r="Y172" s="6" t="inlineStr"/>
-      <c r="Z172" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z172" s="7" t="inlineStr"/>
       <c r="AA172" s="6" t="inlineStr"/>
       <c r="AB172" s="6" t="inlineStr"/>
       <c r="AC172" s="6" t="inlineStr"/>
@@ -15374,7 +15374,11 @@
       <c r="N173" s="7" t="inlineStr"/>
       <c r="O173" s="6" t="inlineStr"/>
       <c r="P173" s="7" t="inlineStr"/>
-      <c r="Q173" s="6" t="inlineStr"/>
+      <c r="Q173" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R173" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15391,11 +15395,7 @@
       <c r="W173" s="6" t="inlineStr"/>
       <c r="X173" s="7" t="inlineStr"/>
       <c r="Y173" s="6" t="inlineStr"/>
-      <c r="Z173" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z173" s="7" t="inlineStr"/>
       <c r="AA173" s="6" t="inlineStr"/>
       <c r="AB173" s="6" t="inlineStr"/>
       <c r="AC173" s="6" t="inlineStr"/>
@@ -15456,7 +15456,11 @@
       <c r="N174" s="7" t="inlineStr"/>
       <c r="O174" s="6" t="inlineStr"/>
       <c r="P174" s="7" t="inlineStr"/>
-      <c r="Q174" s="6" t="inlineStr"/>
+      <c r="Q174" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R174" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15473,11 +15477,7 @@
       <c r="W174" s="6" t="inlineStr"/>
       <c r="X174" s="7" t="inlineStr"/>
       <c r="Y174" s="6" t="inlineStr"/>
-      <c r="Z174" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z174" s="7" t="inlineStr"/>
       <c r="AA174" s="6" t="inlineStr"/>
       <c r="AB174" s="6" t="inlineStr"/>
       <c r="AC174" s="6" t="inlineStr"/>
@@ -15538,7 +15538,11 @@
       <c r="N175" s="7" t="inlineStr"/>
       <c r="O175" s="6" t="inlineStr"/>
       <c r="P175" s="7" t="inlineStr"/>
-      <c r="Q175" s="6" t="inlineStr"/>
+      <c r="Q175" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R175" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15555,11 +15559,7 @@
       <c r="W175" s="6" t="inlineStr"/>
       <c r="X175" s="7" t="inlineStr"/>
       <c r="Y175" s="6" t="inlineStr"/>
-      <c r="Z175" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z175" s="7" t="inlineStr"/>
       <c r="AA175" s="6" t="inlineStr"/>
       <c r="AB175" s="6" t="inlineStr"/>
       <c r="AC175" s="6" t="inlineStr"/>
@@ -15620,7 +15620,11 @@
       <c r="N176" s="7" t="inlineStr"/>
       <c r="O176" s="6" t="inlineStr"/>
       <c r="P176" s="7" t="inlineStr"/>
-      <c r="Q176" s="6" t="inlineStr"/>
+      <c r="Q176" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R176" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15637,11 +15641,7 @@
       <c r="W176" s="6" t="inlineStr"/>
       <c r="X176" s="7" t="inlineStr"/>
       <c r="Y176" s="6" t="inlineStr"/>
-      <c r="Z176" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z176" s="7" t="inlineStr"/>
       <c r="AA176" s="6" t="inlineStr"/>
       <c r="AB176" s="6" t="inlineStr"/>
       <c r="AC176" s="6" t="inlineStr"/>
@@ -15702,7 +15702,11 @@
       <c r="N177" s="7" t="inlineStr"/>
       <c r="O177" s="6" t="inlineStr"/>
       <c r="P177" s="7" t="inlineStr"/>
-      <c r="Q177" s="6" t="inlineStr"/>
+      <c r="Q177" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R177" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15719,11 +15723,7 @@
       <c r="W177" s="6" t="inlineStr"/>
       <c r="X177" s="7" t="inlineStr"/>
       <c r="Y177" s="6" t="inlineStr"/>
-      <c r="Z177" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z177" s="7" t="inlineStr"/>
       <c r="AA177" s="6" t="inlineStr"/>
       <c r="AB177" s="6" t="inlineStr"/>
       <c r="AC177" s="6" t="inlineStr"/>
@@ -15784,7 +15784,11 @@
       <c r="N178" s="7" t="inlineStr"/>
       <c r="O178" s="6" t="inlineStr"/>
       <c r="P178" s="7" t="inlineStr"/>
-      <c r="Q178" s="6" t="inlineStr"/>
+      <c r="Q178" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R178" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15801,11 +15805,7 @@
       <c r="W178" s="6" t="inlineStr"/>
       <c r="X178" s="7" t="inlineStr"/>
       <c r="Y178" s="6" t="inlineStr"/>
-      <c r="Z178" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z178" s="7" t="inlineStr"/>
       <c r="AA178" s="6" t="inlineStr"/>
       <c r="AB178" s="6" t="inlineStr"/>
       <c r="AC178" s="6" t="inlineStr"/>
@@ -15866,7 +15866,11 @@
       <c r="N179" s="7" t="inlineStr"/>
       <c r="O179" s="6" t="inlineStr"/>
       <c r="P179" s="7" t="inlineStr"/>
-      <c r="Q179" s="6" t="inlineStr"/>
+      <c r="Q179" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R179" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15883,11 +15887,7 @@
       <c r="W179" s="6" t="inlineStr"/>
       <c r="X179" s="7" t="inlineStr"/>
       <c r="Y179" s="6" t="inlineStr"/>
-      <c r="Z179" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z179" s="7" t="inlineStr"/>
       <c r="AA179" s="6" t="inlineStr"/>
       <c r="AB179" s="6" t="inlineStr"/>
       <c r="AC179" s="6" t="inlineStr"/>
@@ -15948,7 +15948,11 @@
       <c r="N180" s="7" t="inlineStr"/>
       <c r="O180" s="6" t="inlineStr"/>
       <c r="P180" s="7" t="inlineStr"/>
-      <c r="Q180" s="6" t="inlineStr"/>
+      <c r="Q180" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R180" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -15965,11 +15969,7 @@
       <c r="W180" s="6" t="inlineStr"/>
       <c r="X180" s="7" t="inlineStr"/>
       <c r="Y180" s="6" t="inlineStr"/>
-      <c r="Z180" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z180" s="7" t="inlineStr"/>
       <c r="AA180" s="6" t="inlineStr"/>
       <c r="AB180" s="6" t="inlineStr"/>
       <c r="AC180" s="6" t="inlineStr"/>
@@ -16030,7 +16030,11 @@
       <c r="N181" s="7" t="inlineStr"/>
       <c r="O181" s="6" t="inlineStr"/>
       <c r="P181" s="7" t="inlineStr"/>
-      <c r="Q181" s="6" t="inlineStr"/>
+      <c r="Q181" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R181" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16047,11 +16051,7 @@
       <c r="W181" s="6" t="inlineStr"/>
       <c r="X181" s="7" t="inlineStr"/>
       <c r="Y181" s="6" t="inlineStr"/>
-      <c r="Z181" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z181" s="7" t="inlineStr"/>
       <c r="AA181" s="6" t="inlineStr"/>
       <c r="AB181" s="6" t="inlineStr"/>
       <c r="AC181" s="6" t="inlineStr"/>
@@ -16112,7 +16112,11 @@
       <c r="N182" s="7" t="inlineStr"/>
       <c r="O182" s="6" t="inlineStr"/>
       <c r="P182" s="7" t="inlineStr"/>
-      <c r="Q182" s="6" t="inlineStr"/>
+      <c r="Q182" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R182" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16129,11 +16133,7 @@
       <c r="W182" s="6" t="inlineStr"/>
       <c r="X182" s="7" t="inlineStr"/>
       <c r="Y182" s="6" t="inlineStr"/>
-      <c r="Z182" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z182" s="7" t="inlineStr"/>
       <c r="AA182" s="6" t="inlineStr"/>
       <c r="AB182" s="6" t="inlineStr"/>
       <c r="AC182" s="6" t="inlineStr"/>
@@ -16194,7 +16194,11 @@
       <c r="N183" s="7" t="inlineStr"/>
       <c r="O183" s="6" t="inlineStr"/>
       <c r="P183" s="7" t="inlineStr"/>
-      <c r="Q183" s="6" t="inlineStr"/>
+      <c r="Q183" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R183" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16211,11 +16215,7 @@
       <c r="W183" s="6" t="inlineStr"/>
       <c r="X183" s="7" t="inlineStr"/>
       <c r="Y183" s="6" t="inlineStr"/>
-      <c r="Z183" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z183" s="7" t="inlineStr"/>
       <c r="AA183" s="6" t="inlineStr"/>
       <c r="AB183" s="6" t="inlineStr"/>
       <c r="AC183" s="6" t="inlineStr"/>
@@ -16276,7 +16276,11 @@
       <c r="N184" s="7" t="inlineStr"/>
       <c r="O184" s="6" t="inlineStr"/>
       <c r="P184" s="7" t="inlineStr"/>
-      <c r="Q184" s="6" t="inlineStr"/>
+      <c r="Q184" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R184" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16293,11 +16297,7 @@
       <c r="W184" s="6" t="inlineStr"/>
       <c r="X184" s="7" t="inlineStr"/>
       <c r="Y184" s="6" t="inlineStr"/>
-      <c r="Z184" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z184" s="7" t="inlineStr"/>
       <c r="AA184" s="6" t="inlineStr"/>
       <c r="AB184" s="6" t="inlineStr"/>
       <c r="AC184" s="6" t="inlineStr"/>
@@ -16358,7 +16358,11 @@
       <c r="N185" s="7" t="inlineStr"/>
       <c r="O185" s="6" t="inlineStr"/>
       <c r="P185" s="7" t="inlineStr"/>
-      <c r="Q185" s="6" t="inlineStr"/>
+      <c r="Q185" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R185" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16375,11 +16379,7 @@
       <c r="W185" s="6" t="inlineStr"/>
       <c r="X185" s="7" t="inlineStr"/>
       <c r="Y185" s="6" t="inlineStr"/>
-      <c r="Z185" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z185" s="7" t="inlineStr"/>
       <c r="AA185" s="6" t="inlineStr"/>
       <c r="AB185" s="6" t="inlineStr"/>
       <c r="AC185" s="6" t="inlineStr"/>
@@ -16440,7 +16440,11 @@
       <c r="N186" s="7" t="inlineStr"/>
       <c r="O186" s="6" t="inlineStr"/>
       <c r="P186" s="7" t="inlineStr"/>
-      <c r="Q186" s="6" t="inlineStr"/>
+      <c r="Q186" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R186" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16457,11 +16461,7 @@
       <c r="W186" s="6" t="inlineStr"/>
       <c r="X186" s="7" t="inlineStr"/>
       <c r="Y186" s="6" t="inlineStr"/>
-      <c r="Z186" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z186" s="7" t="inlineStr"/>
       <c r="AA186" s="6" t="inlineStr"/>
       <c r="AB186" s="6" t="inlineStr"/>
       <c r="AC186" s="6" t="inlineStr"/>
@@ -16522,7 +16522,11 @@
       <c r="N187" s="3" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr"/>
       <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="2" t="inlineStr"/>
+      <c r="Q187" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R187" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -16539,11 +16543,7 @@
       <c r="W187" s="2" t="inlineStr"/>
       <c r="X187" s="3" t="inlineStr"/>
       <c r="Y187" s="2" t="inlineStr"/>
-      <c r="Z187" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z187" s="3" t="inlineStr"/>
       <c r="AA187" s="2" t="inlineStr"/>
       <c r="AB187" s="2" t="inlineStr"/>
       <c r="AC187" s="2" t="inlineStr"/>
@@ -16604,7 +16604,11 @@
       <c r="N188" s="7" t="inlineStr"/>
       <c r="O188" s="6" t="inlineStr"/>
       <c r="P188" s="7" t="inlineStr"/>
-      <c r="Q188" s="6" t="inlineStr"/>
+      <c r="Q188" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R188" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16621,11 +16625,7 @@
       <c r="W188" s="6" t="inlineStr"/>
       <c r="X188" s="7" t="inlineStr"/>
       <c r="Y188" s="6" t="inlineStr"/>
-      <c r="Z188" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z188" s="7" t="inlineStr"/>
       <c r="AA188" s="6" t="inlineStr"/>
       <c r="AB188" s="6" t="inlineStr"/>
       <c r="AC188" s="6" t="inlineStr"/>
@@ -16686,7 +16686,11 @@
       <c r="N189" s="3" t="inlineStr"/>
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr"/>
-      <c r="Q189" s="2" t="inlineStr"/>
+      <c r="Q189" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R189" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -16703,11 +16707,7 @@
       <c r="W189" s="2" t="inlineStr"/>
       <c r="X189" s="3" t="inlineStr"/>
       <c r="Y189" s="2" t="inlineStr"/>
-      <c r="Z189" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z189" s="3" t="inlineStr"/>
       <c r="AA189" s="2" t="inlineStr"/>
       <c r="AB189" s="2" t="inlineStr"/>
       <c r="AC189" s="2" t="inlineStr">
@@ -16776,7 +16776,11 @@
       <c r="N190" s="7" t="inlineStr"/>
       <c r="O190" s="6" t="inlineStr"/>
       <c r="P190" s="7" t="inlineStr"/>
-      <c r="Q190" s="6" t="inlineStr"/>
+      <c r="Q190" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R190" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16793,11 +16797,7 @@
       <c r="W190" s="6" t="inlineStr"/>
       <c r="X190" s="7" t="inlineStr"/>
       <c r="Y190" s="6" t="inlineStr"/>
-      <c r="Z190" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z190" s="7" t="inlineStr"/>
       <c r="AA190" s="6" t="inlineStr"/>
       <c r="AB190" s="6" t="inlineStr"/>
       <c r="AC190" s="6" t="inlineStr">
@@ -16866,7 +16866,11 @@
       <c r="N191" s="7" t="inlineStr"/>
       <c r="O191" s="6" t="inlineStr"/>
       <c r="P191" s="7" t="inlineStr"/>
-      <c r="Q191" s="6" t="inlineStr"/>
+      <c r="Q191" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16883,11 +16887,7 @@
       <c r="W191" s="6" t="inlineStr"/>
       <c r="X191" s="7" t="inlineStr"/>
       <c r="Y191" s="6" t="inlineStr"/>
-      <c r="Z191" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z191" s="7" t="inlineStr"/>
       <c r="AA191" s="6" t="inlineStr"/>
       <c r="AB191" s="6" t="inlineStr"/>
       <c r="AC191" s="6" t="inlineStr">
@@ -16956,7 +16956,11 @@
       <c r="N192" s="7" t="inlineStr"/>
       <c r="O192" s="6" t="inlineStr"/>
       <c r="P192" s="7" t="inlineStr"/>
-      <c r="Q192" s="6" t="inlineStr"/>
+      <c r="Q192" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -16973,11 +16977,7 @@
       <c r="W192" s="6" t="inlineStr"/>
       <c r="X192" s="7" t="inlineStr"/>
       <c r="Y192" s="6" t="inlineStr"/>
-      <c r="Z192" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z192" s="7" t="inlineStr"/>
       <c r="AA192" s="6" t="inlineStr"/>
       <c r="AB192" s="6" t="inlineStr"/>
       <c r="AC192" s="6" t="inlineStr">
@@ -17046,7 +17046,11 @@
       <c r="N193" s="3" t="inlineStr"/>
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="3" t="inlineStr"/>
-      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="Q193" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R193" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -17063,11 +17067,7 @@
       <c r="W193" s="2" t="inlineStr"/>
       <c r="X193" s="3" t="inlineStr"/>
       <c r="Y193" s="2" t="inlineStr"/>
-      <c r="Z193" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z193" s="3" t="inlineStr"/>
       <c r="AA193" s="2" t="inlineStr"/>
       <c r="AB193" s="2" t="inlineStr"/>
       <c r="AC193" s="2" t="inlineStr">
@@ -17136,7 +17136,11 @@
       <c r="N194" s="7" t="inlineStr"/>
       <c r="O194" s="6" t="inlineStr"/>
       <c r="P194" s="7" t="inlineStr"/>
-      <c r="Q194" s="6" t="inlineStr"/>
+      <c r="Q194" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -17153,11 +17157,7 @@
       <c r="W194" s="6" t="inlineStr"/>
       <c r="X194" s="7" t="inlineStr"/>
       <c r="Y194" s="6" t="inlineStr"/>
-      <c r="Z194" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z194" s="7" t="inlineStr"/>
       <c r="AA194" s="6" t="inlineStr"/>
       <c r="AB194" s="6" t="inlineStr"/>
       <c r="AC194" s="6" t="inlineStr">
@@ -17226,7 +17226,11 @@
       <c r="N195" s="7" t="inlineStr"/>
       <c r="O195" s="6" t="inlineStr"/>
       <c r="P195" s="7" t="inlineStr"/>
-      <c r="Q195" s="6" t="inlineStr"/>
+      <c r="Q195" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R195" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -17243,11 +17247,7 @@
       <c r="W195" s="6" t="inlineStr"/>
       <c r="X195" s="7" t="inlineStr"/>
       <c r="Y195" s="6" t="inlineStr"/>
-      <c r="Z195" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z195" s="7" t="inlineStr"/>
       <c r="AA195" s="6" t="inlineStr"/>
       <c r="AB195" s="6" t="inlineStr"/>
       <c r="AC195" s="6" t="inlineStr">
@@ -17410,12 +17410,12 @@
       </c>
       <c r="S197" s="2" t="inlineStr"/>
       <c r="T197" s="3" t="inlineStr"/>
-      <c r="U197" s="2" t="inlineStr"/>
-      <c r="V197" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V197" s="3" t="inlineStr"/>
       <c r="W197" s="2" t="inlineStr"/>
       <c r="X197" s="3" t="inlineStr"/>
       <c r="Y197" s="2" t="inlineStr"/>
@@ -17488,12 +17488,12 @@
       </c>
       <c r="S198" s="6" t="inlineStr"/>
       <c r="T198" s="7" t="inlineStr"/>
-      <c r="U198" s="6" t="inlineStr"/>
-      <c r="V198" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U198" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V198" s="7" t="inlineStr"/>
       <c r="W198" s="6" t="inlineStr"/>
       <c r="X198" s="7" t="inlineStr"/>
       <c r="Y198" s="6" t="inlineStr"/>
@@ -17566,12 +17566,12 @@
       </c>
       <c r="S199" s="6" t="inlineStr"/>
       <c r="T199" s="7" t="inlineStr"/>
-      <c r="U199" s="6" t="inlineStr"/>
-      <c r="V199" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U199" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V199" s="7" t="inlineStr"/>
       <c r="W199" s="6" t="inlineStr"/>
       <c r="X199" s="7" t="inlineStr"/>
       <c r="Y199" s="6" t="inlineStr"/>
@@ -17648,12 +17648,12 @@
       </c>
       <c r="S200" s="6" t="inlineStr"/>
       <c r="T200" s="7" t="inlineStr"/>
-      <c r="U200" s="6" t="inlineStr"/>
-      <c r="V200" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U200" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V200" s="7" t="inlineStr"/>
       <c r="W200" s="6" t="inlineStr"/>
       <c r="X200" s="7" t="inlineStr"/>
       <c r="Y200" s="6" t="inlineStr"/>
@@ -17730,12 +17730,12 @@
       </c>
       <c r="S201" s="6" t="inlineStr"/>
       <c r="T201" s="7" t="inlineStr"/>
-      <c r="U201" s="6" t="inlineStr"/>
-      <c r="V201" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U201" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V201" s="7" t="inlineStr"/>
       <c r="W201" s="6" t="inlineStr"/>
       <c r="X201" s="7" t="inlineStr"/>
       <c r="Y201" s="6" t="inlineStr"/>
@@ -17808,12 +17808,12 @@
       </c>
       <c r="S202" s="6" t="inlineStr"/>
       <c r="T202" s="7" t="inlineStr"/>
-      <c r="U202" s="6" t="inlineStr"/>
-      <c r="V202" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U202" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V202" s="7" t="inlineStr"/>
       <c r="W202" s="6" t="inlineStr"/>
       <c r="X202" s="7" t="inlineStr"/>
       <c r="Y202" s="6" t="inlineStr"/>
@@ -17886,12 +17886,12 @@
       </c>
       <c r="S203" s="6" t="inlineStr"/>
       <c r="T203" s="7" t="inlineStr"/>
-      <c r="U203" s="6" t="inlineStr"/>
-      <c r="V203" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U203" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V203" s="7" t="inlineStr"/>
       <c r="W203" s="6" t="inlineStr"/>
       <c r="X203" s="7" t="inlineStr"/>
       <c r="Y203" s="6" t="inlineStr"/>
@@ -17964,12 +17964,12 @@
       </c>
       <c r="S204" s="6" t="inlineStr"/>
       <c r="T204" s="7" t="inlineStr"/>
-      <c r="U204" s="6" t="inlineStr"/>
-      <c r="V204" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U204" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V204" s="7" t="inlineStr"/>
       <c r="W204" s="6" t="inlineStr"/>
       <c r="X204" s="7" t="inlineStr"/>
       <c r="Y204" s="6" t="inlineStr"/>
@@ -18042,12 +18042,12 @@
       </c>
       <c r="S205" s="2" t="inlineStr"/>
       <c r="T205" s="3" t="inlineStr"/>
-      <c r="U205" s="2" t="inlineStr"/>
-      <c r="V205" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V205" s="3" t="inlineStr"/>
       <c r="W205" s="2" t="inlineStr"/>
       <c r="X205" s="3" t="inlineStr"/>
       <c r="Y205" s="2" t="inlineStr"/>
@@ -18124,12 +18124,12 @@
       </c>
       <c r="S206" s="6" t="inlineStr"/>
       <c r="T206" s="7" t="inlineStr"/>
-      <c r="U206" s="6" t="inlineStr"/>
-      <c r="V206" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U206" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V206" s="7" t="inlineStr"/>
       <c r="W206" s="6" t="inlineStr"/>
       <c r="X206" s="7" t="inlineStr"/>
       <c r="Y206" s="6" t="inlineStr"/>
@@ -18206,12 +18206,12 @@
       </c>
       <c r="S207" s="6" t="inlineStr"/>
       <c r="T207" s="7" t="inlineStr"/>
-      <c r="U207" s="6" t="inlineStr"/>
-      <c r="V207" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U207" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V207" s="7" t="inlineStr"/>
       <c r="W207" s="6" t="inlineStr"/>
       <c r="X207" s="7" t="inlineStr"/>
       <c r="Y207" s="6" t="inlineStr"/>
@@ -18288,12 +18288,12 @@
       </c>
       <c r="S208" s="2" t="inlineStr"/>
       <c r="T208" s="3" t="inlineStr"/>
-      <c r="U208" s="2" t="inlineStr"/>
-      <c r="V208" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V208" s="3" t="inlineStr"/>
       <c r="W208" s="2" t="inlineStr">
         <is>
           <t>r</t>
@@ -18372,12 +18372,12 @@
       </c>
       <c r="S209" s="6" t="inlineStr"/>
       <c r="T209" s="7" t="inlineStr"/>
-      <c r="U209" s="6" t="inlineStr"/>
-      <c r="V209" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U209" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V209" s="7" t="inlineStr"/>
       <c r="W209" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18456,12 +18456,12 @@
       </c>
       <c r="S210" s="6" t="inlineStr"/>
       <c r="T210" s="7" t="inlineStr"/>
-      <c r="U210" s="6" t="inlineStr"/>
-      <c r="V210" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U210" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V210" s="7" t="inlineStr"/>
       <c r="W210" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18540,12 +18540,12 @@
       </c>
       <c r="S211" s="6" t="inlineStr"/>
       <c r="T211" s="7" t="inlineStr"/>
-      <c r="U211" s="6" t="inlineStr"/>
-      <c r="V211" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U211" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V211" s="7" t="inlineStr"/>
       <c r="W211" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18624,12 +18624,12 @@
       </c>
       <c r="S212" s="6" t="inlineStr"/>
       <c r="T212" s="7" t="inlineStr"/>
-      <c r="U212" s="6" t="inlineStr"/>
-      <c r="V212" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U212" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V212" s="7" t="inlineStr"/>
       <c r="W212" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18708,12 +18708,12 @@
       </c>
       <c r="S213" s="6" t="inlineStr"/>
       <c r="T213" s="7" t="inlineStr"/>
-      <c r="U213" s="6" t="inlineStr"/>
-      <c r="V213" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U213" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V213" s="7" t="inlineStr"/>
       <c r="W213" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18792,12 +18792,12 @@
       </c>
       <c r="S214" s="6" t="inlineStr"/>
       <c r="T214" s="7" t="inlineStr"/>
-      <c r="U214" s="6" t="inlineStr"/>
-      <c r="V214" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U214" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V214" s="7" t="inlineStr"/>
       <c r="W214" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18876,12 +18876,12 @@
       </c>
       <c r="S215" s="6" t="inlineStr"/>
       <c r="T215" s="7" t="inlineStr"/>
-      <c r="U215" s="6" t="inlineStr"/>
-      <c r="V215" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U215" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V215" s="7" t="inlineStr"/>
       <c r="W215" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -18960,12 +18960,12 @@
       </c>
       <c r="S216" s="6" t="inlineStr"/>
       <c r="T216" s="7" t="inlineStr"/>
-      <c r="U216" s="6" t="inlineStr"/>
-      <c r="V216" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U216" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V216" s="7" t="inlineStr"/>
       <c r="W216" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19044,12 +19044,12 @@
       </c>
       <c r="S217" s="6" t="inlineStr"/>
       <c r="T217" s="7" t="inlineStr"/>
-      <c r="U217" s="6" t="inlineStr"/>
-      <c r="V217" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U217" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V217" s="7" t="inlineStr"/>
       <c r="W217" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19128,12 +19128,12 @@
       </c>
       <c r="S218" s="6" t="inlineStr"/>
       <c r="T218" s="7" t="inlineStr"/>
-      <c r="U218" s="6" t="inlineStr"/>
-      <c r="V218" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U218" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V218" s="7" t="inlineStr"/>
       <c r="W218" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19212,12 +19212,12 @@
       </c>
       <c r="S219" s="6" t="inlineStr"/>
       <c r="T219" s="7" t="inlineStr"/>
-      <c r="U219" s="6" t="inlineStr"/>
-      <c r="V219" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U219" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V219" s="7" t="inlineStr"/>
       <c r="W219" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19296,12 +19296,12 @@
       </c>
       <c r="S220" s="6" t="inlineStr"/>
       <c r="T220" s="7" t="inlineStr"/>
-      <c r="U220" s="6" t="inlineStr"/>
-      <c r="V220" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U220" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V220" s="7" t="inlineStr"/>
       <c r="W220" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19380,12 +19380,12 @@
       </c>
       <c r="S221" s="6" t="inlineStr"/>
       <c r="T221" s="7" t="inlineStr"/>
-      <c r="U221" s="6" t="inlineStr"/>
-      <c r="V221" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U221" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V221" s="7" t="inlineStr"/>
       <c r="W221" s="6" t="inlineStr">
         <is>
           <t>r</t>
@@ -19464,12 +19464,12 @@
       </c>
       <c r="S222" s="6" t="inlineStr"/>
       <c r="T222" s="7" t="inlineStr"/>
-      <c r="U222" s="6" t="inlineStr"/>
-      <c r="V222" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U222" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V222" s="7" t="inlineStr"/>
       <c r="W222" s="6" t="inlineStr"/>
       <c r="X222" s="7" t="inlineStr"/>
       <c r="Y222" s="6" t="inlineStr"/>
@@ -19538,12 +19538,12 @@
       </c>
       <c r="S223" s="6" t="inlineStr"/>
       <c r="T223" s="7" t="inlineStr"/>
-      <c r="U223" s="6" t="inlineStr"/>
-      <c r="V223" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U223" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V223" s="7" t="inlineStr"/>
       <c r="W223" s="6" t="inlineStr"/>
       <c r="X223" s="7" t="inlineStr"/>
       <c r="Y223" s="6" t="inlineStr"/>
@@ -19618,12 +19618,12 @@
       </c>
       <c r="S224" s="6" t="inlineStr"/>
       <c r="T224" s="7" t="inlineStr"/>
-      <c r="U224" s="6" t="inlineStr"/>
-      <c r="V224" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U224" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V224" s="7" t="inlineStr"/>
       <c r="W224" s="6" t="inlineStr"/>
       <c r="X224" s="7" t="inlineStr"/>
       <c r="Y224" s="6" t="inlineStr"/>
@@ -19698,12 +19698,12 @@
       </c>
       <c r="S225" s="6" t="inlineStr"/>
       <c r="T225" s="7" t="inlineStr"/>
-      <c r="U225" s="6" t="inlineStr"/>
-      <c r="V225" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U225" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V225" s="7" t="inlineStr"/>
       <c r="W225" s="6" t="inlineStr"/>
       <c r="X225" s="7" t="inlineStr"/>
       <c r="Y225" s="6" t="inlineStr"/>
@@ -19778,12 +19778,12 @@
       </c>
       <c r="S226" s="6" t="inlineStr"/>
       <c r="T226" s="7" t="inlineStr"/>
-      <c r="U226" s="6" t="inlineStr"/>
-      <c r="V226" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U226" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V226" s="7" t="inlineStr"/>
       <c r="W226" s="6" t="inlineStr"/>
       <c r="X226" s="7" t="inlineStr"/>
       <c r="Y226" s="6" t="inlineStr"/>
@@ -19856,12 +19856,12 @@
       </c>
       <c r="S227" s="6" t="inlineStr"/>
       <c r="T227" s="7" t="inlineStr"/>
-      <c r="U227" s="6" t="inlineStr"/>
-      <c r="V227" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U227" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V227" s="7" t="inlineStr"/>
       <c r="W227" s="6" t="inlineStr"/>
       <c r="X227" s="7" t="inlineStr"/>
       <c r="Y227" s="6" t="inlineStr"/>
@@ -19934,12 +19934,12 @@
       </c>
       <c r="S228" s="6" t="inlineStr"/>
       <c r="T228" s="7" t="inlineStr"/>
-      <c r="U228" s="6" t="inlineStr"/>
-      <c r="V228" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U228" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V228" s="7" t="inlineStr"/>
       <c r="W228" s="6" t="inlineStr"/>
       <c r="X228" s="7" t="inlineStr"/>
       <c r="Y228" s="6" t="inlineStr"/>
@@ -20021,16 +20021,16 @@
         </is>
       </c>
       <c r="U229" s="2" t="inlineStr"/>
-      <c r="V229" s="3" t="inlineStr"/>
+      <c r="V229" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W229" s="2" t="inlineStr"/>
       <c r="X229" s="3" t="inlineStr"/>
       <c r="Y229" s="2" t="inlineStr"/>
       <c r="Z229" s="3" t="inlineStr"/>
-      <c r="AA229" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA229" s="2" t="inlineStr"/>
       <c r="AB229" s="2" t="inlineStr"/>
       <c r="AC229" s="2" t="inlineStr">
         <is>
@@ -20107,16 +20107,16 @@
         </is>
       </c>
       <c r="U230" s="6" t="inlineStr"/>
-      <c r="V230" s="7" t="inlineStr"/>
+      <c r="V230" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W230" s="6" t="inlineStr"/>
       <c r="X230" s="7" t="inlineStr"/>
       <c r="Y230" s="6" t="inlineStr"/>
       <c r="Z230" s="7" t="inlineStr"/>
-      <c r="AA230" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA230" s="6" t="inlineStr"/>
       <c r="AB230" s="6" t="inlineStr"/>
       <c r="AC230" s="6" t="inlineStr"/>
       <c r="AD230" s="6" t="inlineStr"/>
@@ -20189,16 +20189,16 @@
         </is>
       </c>
       <c r="U231" s="6" t="inlineStr"/>
-      <c r="V231" s="7" t="inlineStr"/>
+      <c r="V231" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W231" s="6" t="inlineStr"/>
       <c r="X231" s="7" t="inlineStr"/>
       <c r="Y231" s="6" t="inlineStr"/>
       <c r="Z231" s="7" t="inlineStr"/>
-      <c r="AA231" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA231" s="6" t="inlineStr"/>
       <c r="AB231" s="6" t="inlineStr"/>
       <c r="AC231" s="6" t="inlineStr"/>
       <c r="AD231" s="6" t="inlineStr"/>
@@ -20271,16 +20271,16 @@
         </is>
       </c>
       <c r="U232" s="6" t="inlineStr"/>
-      <c r="V232" s="7" t="inlineStr"/>
+      <c r="V232" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W232" s="6" t="inlineStr"/>
       <c r="X232" s="7" t="inlineStr"/>
       <c r="Y232" s="6" t="inlineStr"/>
       <c r="Z232" s="7" t="inlineStr"/>
-      <c r="AA232" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA232" s="6" t="inlineStr"/>
       <c r="AB232" s="6" t="inlineStr"/>
       <c r="AC232" s="6" t="inlineStr">
         <is>
@@ -20361,16 +20361,16 @@
         </is>
       </c>
       <c r="U233" s="6" t="inlineStr"/>
-      <c r="V233" s="7" t="inlineStr"/>
+      <c r="V233" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W233" s="6" t="inlineStr"/>
       <c r="X233" s="7" t="inlineStr"/>
       <c r="Y233" s="6" t="inlineStr"/>
       <c r="Z233" s="7" t="inlineStr"/>
-      <c r="AA233" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA233" s="6" t="inlineStr"/>
       <c r="AB233" s="6" t="inlineStr"/>
       <c r="AC233" s="6" t="inlineStr">
         <is>
@@ -20451,16 +20451,16 @@
         </is>
       </c>
       <c r="U234" s="6" t="inlineStr"/>
-      <c r="V234" s="7" t="inlineStr"/>
+      <c r="V234" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W234" s="6" t="inlineStr"/>
       <c r="X234" s="7" t="inlineStr"/>
       <c r="Y234" s="6" t="inlineStr"/>
       <c r="Z234" s="7" t="inlineStr"/>
-      <c r="AA234" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA234" s="6" t="inlineStr"/>
       <c r="AB234" s="6" t="inlineStr"/>
       <c r="AC234" s="6" t="inlineStr">
         <is>
@@ -20537,16 +20537,16 @@
         </is>
       </c>
       <c r="U235" s="6" t="inlineStr"/>
-      <c r="V235" s="7" t="inlineStr"/>
+      <c r="V235" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W235" s="6" t="inlineStr"/>
       <c r="X235" s="7" t="inlineStr"/>
       <c r="Y235" s="6" t="inlineStr"/>
       <c r="Z235" s="7" t="inlineStr"/>
-      <c r="AA235" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA235" s="6" t="inlineStr"/>
       <c r="AB235" s="6" t="inlineStr"/>
       <c r="AC235" s="6" t="inlineStr"/>
       <c r="AD235" s="6" t="inlineStr"/>
@@ -20619,16 +20619,16 @@
         </is>
       </c>
       <c r="U236" s="6" t="inlineStr"/>
-      <c r="V236" s="7" t="inlineStr"/>
+      <c r="V236" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W236" s="6" t="inlineStr"/>
       <c r="X236" s="7" t="inlineStr"/>
       <c r="Y236" s="6" t="inlineStr"/>
       <c r="Z236" s="7" t="inlineStr"/>
-      <c r="AA236" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA236" s="6" t="inlineStr"/>
       <c r="AB236" s="6" t="inlineStr"/>
       <c r="AC236" s="6" t="inlineStr"/>
       <c r="AD236" s="6" t="inlineStr"/>
@@ -20701,16 +20701,16 @@
         </is>
       </c>
       <c r="U237" s="6" t="inlineStr"/>
-      <c r="V237" s="7" t="inlineStr"/>
+      <c r="V237" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W237" s="6" t="inlineStr"/>
       <c r="X237" s="7" t="inlineStr"/>
       <c r="Y237" s="6" t="inlineStr"/>
       <c r="Z237" s="7" t="inlineStr"/>
-      <c r="AA237" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA237" s="6" t="inlineStr"/>
       <c r="AB237" s="6" t="inlineStr"/>
       <c r="AC237" s="6" t="inlineStr">
         <is>
@@ -20791,16 +20791,16 @@
         </is>
       </c>
       <c r="U238" s="6" t="inlineStr"/>
-      <c r="V238" s="7" t="inlineStr"/>
+      <c r="V238" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W238" s="6" t="inlineStr"/>
       <c r="X238" s="7" t="inlineStr"/>
       <c r="Y238" s="6" t="inlineStr"/>
       <c r="Z238" s="7" t="inlineStr"/>
-      <c r="AA238" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA238" s="6" t="inlineStr"/>
       <c r="AB238" s="6" t="inlineStr"/>
       <c r="AC238" s="6" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>The voltage of the front brake pressure sensor expressed in mV</t>
+          <t>Front brake pressure expressed in bar</t>
         </is>
       </c>
       <c r="J239" s="2" t="n">
@@ -20865,11 +20865,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N239" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="N239" s="3" t="inlineStr"/>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="3" t="inlineStr"/>
       <c r="Q239" s="2" t="inlineStr"/>
@@ -20880,26 +20876,30 @@
       </c>
       <c r="S239" s="2" t="inlineStr"/>
       <c r="T239" s="3" t="inlineStr"/>
-      <c r="U239" s="2" t="inlineStr"/>
-      <c r="V239" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U239" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V239" s="3" t="inlineStr"/>
       <c r="W239" s="2" t="inlineStr"/>
-      <c r="X239" s="3" t="inlineStr"/>
+      <c r="X239" s="3" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Y239" s="2" t="inlineStr"/>
       <c r="Z239" s="3" t="inlineStr"/>
       <c r="AA239" s="2" t="inlineStr"/>
       <c r="AB239" s="2" t="inlineStr"/>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>0..8192</t>
+          <t>0..200</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>mV</t>
+          <t>0.025  bar</t>
         </is>
       </c>
     </row>
@@ -20955,11 +20955,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N240" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="N240" s="7" t="inlineStr"/>
       <c r="O240" s="6" t="inlineStr"/>
       <c r="P240" s="7" t="inlineStr"/>
       <c r="Q240" s="6" t="inlineStr"/>
@@ -20970,14 +20966,18 @@
       </c>
       <c r="S240" s="6" t="inlineStr"/>
       <c r="T240" s="7" t="inlineStr"/>
-      <c r="U240" s="6" t="inlineStr"/>
-      <c r="V240" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U240" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V240" s="7" t="inlineStr"/>
       <c r="W240" s="6" t="inlineStr"/>
-      <c r="X240" s="7" t="inlineStr"/>
+      <c r="X240" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Y240" s="6" t="inlineStr"/>
       <c r="Z240" s="7" t="inlineStr"/>
       <c r="AA240" s="6" t="inlineStr"/>
@@ -21045,11 +21045,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N241" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="N241" s="7" t="inlineStr"/>
       <c r="O241" s="6" t="inlineStr"/>
       <c r="P241" s="7" t="inlineStr"/>
       <c r="Q241" s="6" t="inlineStr"/>
@@ -21060,14 +21056,18 @@
       </c>
       <c r="S241" s="6" t="inlineStr"/>
       <c r="T241" s="7" t="inlineStr"/>
-      <c r="U241" s="6" t="inlineStr"/>
-      <c r="V241" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U241" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V241" s="7" t="inlineStr"/>
       <c r="W241" s="6" t="inlineStr"/>
-      <c r="X241" s="7" t="inlineStr"/>
+      <c r="X241" s="7" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Y241" s="6" t="inlineStr"/>
       <c r="Z241" s="7" t="inlineStr"/>
       <c r="AA241" s="6" t="inlineStr"/>
@@ -21116,7 +21116,7 @@
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>The voltage of the rear brake pressure sensor expressed in mV</t>
+          <t>Rear brake pressure expressed in bar</t>
         </is>
       </c>
       <c r="J242" s="6" t="n">
@@ -21136,11 +21136,7 @@
         </is>
       </c>
       <c r="N242" s="7" t="inlineStr"/>
-      <c r="O242" s="6" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="O242" s="6" t="inlineStr"/>
       <c r="P242" s="7" t="inlineStr"/>
       <c r="Q242" s="6" t="inlineStr"/>
       <c r="R242" s="8" t="inlineStr">
@@ -21150,26 +21146,30 @@
       </c>
       <c r="S242" s="6" t="inlineStr"/>
       <c r="T242" s="7" t="inlineStr"/>
-      <c r="U242" s="6" t="inlineStr"/>
-      <c r="V242" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="U242" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="V242" s="7" t="inlineStr"/>
       <c r="W242" s="6" t="inlineStr"/>
       <c r="X242" s="7" t="inlineStr"/>
-      <c r="Y242" s="6" t="inlineStr"/>
+      <c r="Y242" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="Z242" s="7" t="inlineStr"/>
       <c r="AA242" s="6" t="inlineStr"/>
       <c r="AB242" s="6" t="inlineStr"/>
       <c r="AC242" s="6" t="inlineStr">
         <is>
-          <t>0..65535</t>
+          <t>0..200</t>
         </is>
       </c>
       <c r="AD242" s="6" t="inlineStr">
         <is>
-          <t>mV</t>
+          <t>0.025  bar</t>
         </is>
       </c>
     </row>
@@ -21241,16 +21241,16 @@
         </is>
       </c>
       <c r="U243" s="2" t="inlineStr"/>
-      <c r="V243" s="3" t="inlineStr"/>
+      <c r="V243" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W243" s="2" t="inlineStr"/>
       <c r="X243" s="3" t="inlineStr"/>
       <c r="Y243" s="2" t="inlineStr"/>
       <c r="Z243" s="3" t="inlineStr"/>
-      <c r="AA243" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA243" s="2" t="inlineStr"/>
       <c r="AB243" s="2" t="inlineStr"/>
       <c r="AC243" s="2" t="inlineStr">
         <is>
@@ -21327,16 +21327,16 @@
         </is>
       </c>
       <c r="U244" s="6" t="inlineStr"/>
-      <c r="V244" s="7" t="inlineStr"/>
+      <c r="V244" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W244" s="6" t="inlineStr"/>
       <c r="X244" s="7" t="inlineStr"/>
       <c r="Y244" s="6" t="inlineStr"/>
       <c r="Z244" s="7" t="inlineStr"/>
-      <c r="AA244" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA244" s="6" t="inlineStr"/>
       <c r="AB244" s="6" t="inlineStr"/>
       <c r="AC244" s="6" t="inlineStr"/>
       <c r="AD244" s="6" t="inlineStr"/>
@@ -21409,16 +21409,16 @@
         </is>
       </c>
       <c r="U245" s="6" t="inlineStr"/>
-      <c r="V245" s="7" t="inlineStr"/>
+      <c r="V245" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W245" s="6" t="inlineStr"/>
       <c r="X245" s="7" t="inlineStr"/>
       <c r="Y245" s="6" t="inlineStr"/>
       <c r="Z245" s="7" t="inlineStr"/>
-      <c r="AA245" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA245" s="6" t="inlineStr"/>
       <c r="AB245" s="6" t="inlineStr"/>
       <c r="AC245" s="6" t="inlineStr"/>
       <c r="AD245" s="6" t="inlineStr"/>
@@ -21491,16 +21491,16 @@
         </is>
       </c>
       <c r="U246" s="6" t="inlineStr"/>
-      <c r="V246" s="7" t="inlineStr"/>
+      <c r="V246" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W246" s="6" t="inlineStr"/>
       <c r="X246" s="7" t="inlineStr"/>
       <c r="Y246" s="6" t="inlineStr"/>
       <c r="Z246" s="7" t="inlineStr"/>
-      <c r="AA246" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA246" s="6" t="inlineStr"/>
       <c r="AB246" s="6" t="inlineStr"/>
       <c r="AC246" s="6" t="inlineStr">
         <is>
@@ -21581,16 +21581,16 @@
         </is>
       </c>
       <c r="U247" s="6" t="inlineStr"/>
-      <c r="V247" s="7" t="inlineStr"/>
+      <c r="V247" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W247" s="6" t="inlineStr"/>
       <c r="X247" s="7" t="inlineStr"/>
       <c r="Y247" s="6" t="inlineStr"/>
       <c r="Z247" s="7" t="inlineStr"/>
-      <c r="AA247" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA247" s="6" t="inlineStr"/>
       <c r="AB247" s="6" t="inlineStr"/>
       <c r="AC247" s="6" t="inlineStr">
         <is>
@@ -21671,16 +21671,16 @@
         </is>
       </c>
       <c r="U248" s="6" t="inlineStr"/>
-      <c r="V248" s="7" t="inlineStr"/>
+      <c r="V248" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W248" s="6" t="inlineStr"/>
       <c r="X248" s="7" t="inlineStr"/>
       <c r="Y248" s="6" t="inlineStr"/>
       <c r="Z248" s="7" t="inlineStr"/>
-      <c r="AA248" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA248" s="6" t="inlineStr"/>
       <c r="AB248" s="6" t="inlineStr"/>
       <c r="AC248" s="6" t="inlineStr">
         <is>
@@ -21757,16 +21757,16 @@
         </is>
       </c>
       <c r="U249" s="6" t="inlineStr"/>
-      <c r="V249" s="7" t="inlineStr"/>
+      <c r="V249" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W249" s="6" t="inlineStr"/>
       <c r="X249" s="7" t="inlineStr"/>
       <c r="Y249" s="6" t="inlineStr"/>
       <c r="Z249" s="7" t="inlineStr"/>
-      <c r="AA249" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA249" s="6" t="inlineStr"/>
       <c r="AB249" s="6" t="inlineStr"/>
       <c r="AC249" s="6" t="inlineStr"/>
       <c r="AD249" s="6" t="inlineStr"/>
@@ -21839,16 +21839,16 @@
         </is>
       </c>
       <c r="U250" s="6" t="inlineStr"/>
-      <c r="V250" s="7" t="inlineStr"/>
+      <c r="V250" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W250" s="6" t="inlineStr"/>
       <c r="X250" s="7" t="inlineStr"/>
       <c r="Y250" s="6" t="inlineStr"/>
       <c r="Z250" s="7" t="inlineStr"/>
-      <c r="AA250" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA250" s="6" t="inlineStr"/>
       <c r="AB250" s="6" t="inlineStr"/>
       <c r="AC250" s="6" t="inlineStr"/>
       <c r="AD250" s="6" t="inlineStr"/>
@@ -21921,16 +21921,16 @@
         </is>
       </c>
       <c r="U251" s="6" t="inlineStr"/>
-      <c r="V251" s="7" t="inlineStr"/>
+      <c r="V251" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W251" s="6" t="inlineStr"/>
       <c r="X251" s="7" t="inlineStr"/>
       <c r="Y251" s="6" t="inlineStr"/>
       <c r="Z251" s="7" t="inlineStr"/>
-      <c r="AA251" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA251" s="6" t="inlineStr"/>
       <c r="AB251" s="6" t="inlineStr"/>
       <c r="AC251" s="6" t="inlineStr">
         <is>
@@ -22011,16 +22011,16 @@
         </is>
       </c>
       <c r="U252" s="6" t="inlineStr"/>
-      <c r="V252" s="7" t="inlineStr"/>
+      <c r="V252" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="W252" s="6" t="inlineStr"/>
       <c r="X252" s="7" t="inlineStr"/>
       <c r="Y252" s="6" t="inlineStr"/>
       <c r="Z252" s="7" t="inlineStr"/>
-      <c r="AA252" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="AA252" s="6" t="inlineStr"/>
       <c r="AB252" s="6" t="inlineStr"/>
       <c r="AC252" s="6" t="inlineStr">
         <is>
@@ -22087,7 +22087,11 @@
       </c>
       <c r="N253" s="3" t="inlineStr"/>
       <c r="O253" s="2" t="inlineStr"/>
-      <c r="P253" s="3" t="inlineStr"/>
+      <c r="P253" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q253" s="2" t="inlineStr"/>
       <c r="R253" s="3" t="inlineStr"/>
       <c r="S253" s="2" t="inlineStr"/>
@@ -22096,11 +22100,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U253" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" s="3" t="inlineStr"/>
       <c r="W253" s="2" t="inlineStr"/>
       <c r="X253" s="3" t="inlineStr"/>
@@ -22165,7 +22165,11 @@
       </c>
       <c r="N254" s="7" t="inlineStr"/>
       <c r="O254" s="6" t="inlineStr"/>
-      <c r="P254" s="7" t="inlineStr"/>
+      <c r="P254" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q254" s="6" t="inlineStr"/>
       <c r="R254" s="7" t="inlineStr"/>
       <c r="S254" s="6" t="inlineStr"/>
@@ -22174,11 +22178,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U254" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U254" s="6" t="inlineStr"/>
       <c r="V254" s="7" t="inlineStr"/>
       <c r="W254" s="6" t="inlineStr"/>
       <c r="X254" s="7" t="inlineStr"/>
@@ -22243,7 +22243,11 @@
       </c>
       <c r="N255" s="7" t="inlineStr"/>
       <c r="O255" s="6" t="inlineStr"/>
-      <c r="P255" s="7" t="inlineStr"/>
+      <c r="P255" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q255" s="6" t="inlineStr"/>
       <c r="R255" s="7" t="inlineStr"/>
       <c r="S255" s="6" t="inlineStr"/>
@@ -22252,11 +22256,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U255" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U255" s="6" t="inlineStr"/>
       <c r="V255" s="7" t="inlineStr"/>
       <c r="W255" s="6" t="inlineStr"/>
       <c r="X255" s="7" t="inlineStr"/>
@@ -22321,7 +22321,11 @@
       </c>
       <c r="N256" s="7" t="inlineStr"/>
       <c r="O256" s="6" t="inlineStr"/>
-      <c r="P256" s="7" t="inlineStr"/>
+      <c r="P256" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q256" s="6" t="inlineStr"/>
       <c r="R256" s="7" t="inlineStr"/>
       <c r="S256" s="6" t="inlineStr"/>
@@ -22330,11 +22334,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U256" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U256" s="6" t="inlineStr"/>
       <c r="V256" s="7" t="inlineStr"/>
       <c r="W256" s="6" t="inlineStr"/>
       <c r="X256" s="7" t="inlineStr"/>
@@ -22399,7 +22399,11 @@
       </c>
       <c r="N257" s="7" t="inlineStr"/>
       <c r="O257" s="6" t="inlineStr"/>
-      <c r="P257" s="7" t="inlineStr"/>
+      <c r="P257" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q257" s="6" t="inlineStr"/>
       <c r="R257" s="7" t="inlineStr"/>
       <c r="S257" s="6" t="inlineStr"/>
@@ -22408,11 +22412,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U257" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U257" s="6" t="inlineStr"/>
       <c r="V257" s="7" t="inlineStr"/>
       <c r="W257" s="6" t="inlineStr"/>
       <c r="X257" s="7" t="inlineStr"/>
@@ -22477,7 +22477,11 @@
       </c>
       <c r="N258" s="7" t="inlineStr"/>
       <c r="O258" s="6" t="inlineStr"/>
-      <c r="P258" s="7" t="inlineStr"/>
+      <c r="P258" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q258" s="6" t="inlineStr"/>
       <c r="R258" s="7" t="inlineStr"/>
       <c r="S258" s="6" t="inlineStr"/>
@@ -22486,11 +22490,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U258" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U258" s="6" t="inlineStr"/>
       <c r="V258" s="7" t="inlineStr"/>
       <c r="W258" s="6" t="inlineStr"/>
       <c r="X258" s="7" t="inlineStr"/>
@@ -22555,7 +22555,11 @@
       </c>
       <c r="N259" s="7" t="inlineStr"/>
       <c r="O259" s="6" t="inlineStr"/>
-      <c r="P259" s="7" t="inlineStr"/>
+      <c r="P259" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q259" s="6" t="inlineStr"/>
       <c r="R259" s="7" t="inlineStr"/>
       <c r="S259" s="6" t="inlineStr"/>
@@ -22564,11 +22568,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U259" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U259" s="6" t="inlineStr"/>
       <c r="V259" s="7" t="inlineStr"/>
       <c r="W259" s="6" t="inlineStr"/>
       <c r="X259" s="7" t="inlineStr"/>
@@ -22633,7 +22633,11 @@
       </c>
       <c r="N260" s="7" t="inlineStr"/>
       <c r="O260" s="6" t="inlineStr"/>
-      <c r="P260" s="7" t="inlineStr"/>
+      <c r="P260" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q260" s="6" t="inlineStr"/>
       <c r="R260" s="7" t="inlineStr"/>
       <c r="S260" s="6" t="inlineStr"/>
@@ -22642,11 +22646,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U260" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U260" s="6" t="inlineStr"/>
       <c r="V260" s="7" t="inlineStr"/>
       <c r="W260" s="6" t="inlineStr"/>
       <c r="X260" s="7" t="inlineStr"/>
@@ -22711,7 +22711,11 @@
       </c>
       <c r="N261" s="7" t="inlineStr"/>
       <c r="O261" s="6" t="inlineStr"/>
-      <c r="P261" s="7" t="inlineStr"/>
+      <c r="P261" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q261" s="6" t="inlineStr"/>
       <c r="R261" s="7" t="inlineStr"/>
       <c r="S261" s="6" t="inlineStr"/>
@@ -22720,11 +22724,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U261" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U261" s="6" t="inlineStr"/>
       <c r="V261" s="7" t="inlineStr"/>
       <c r="W261" s="6" t="inlineStr"/>
       <c r="X261" s="7" t="inlineStr"/>
@@ -22789,7 +22789,11 @@
       </c>
       <c r="N262" s="7" t="inlineStr"/>
       <c r="O262" s="6" t="inlineStr"/>
-      <c r="P262" s="7" t="inlineStr"/>
+      <c r="P262" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q262" s="6" t="inlineStr"/>
       <c r="R262" s="7" t="inlineStr"/>
       <c r="S262" s="6" t="inlineStr"/>
@@ -22798,11 +22802,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U262" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U262" s="6" t="inlineStr"/>
       <c r="V262" s="7" t="inlineStr"/>
       <c r="W262" s="6" t="inlineStr"/>
       <c r="X262" s="7" t="inlineStr"/>
@@ -22867,7 +22867,11 @@
       </c>
       <c r="N263" s="7" t="inlineStr"/>
       <c r="O263" s="6" t="inlineStr"/>
-      <c r="P263" s="7" t="inlineStr"/>
+      <c r="P263" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q263" s="6" t="inlineStr"/>
       <c r="R263" s="7" t="inlineStr"/>
       <c r="S263" s="6" t="inlineStr"/>
@@ -22876,11 +22880,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U263" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U263" s="6" t="inlineStr"/>
       <c r="V263" s="7" t="inlineStr"/>
       <c r="W263" s="6" t="inlineStr"/>
       <c r="X263" s="7" t="inlineStr"/>
@@ -22945,7 +22945,11 @@
       </c>
       <c r="N264" s="7" t="inlineStr"/>
       <c r="O264" s="6" t="inlineStr"/>
-      <c r="P264" s="7" t="inlineStr"/>
+      <c r="P264" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q264" s="6" t="inlineStr"/>
       <c r="R264" s="7" t="inlineStr"/>
       <c r="S264" s="6" t="inlineStr"/>
@@ -22954,11 +22958,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U264" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U264" s="6" t="inlineStr"/>
       <c r="V264" s="7" t="inlineStr"/>
       <c r="W264" s="6" t="inlineStr"/>
       <c r="X264" s="7" t="inlineStr"/>
@@ -23023,7 +23023,11 @@
       </c>
       <c r="N265" s="7" t="inlineStr"/>
       <c r="O265" s="6" t="inlineStr"/>
-      <c r="P265" s="7" t="inlineStr"/>
+      <c r="P265" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q265" s="6" t="inlineStr"/>
       <c r="R265" s="7" t="inlineStr"/>
       <c r="S265" s="6" t="inlineStr"/>
@@ -23032,11 +23036,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U265" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U265" s="6" t="inlineStr"/>
       <c r="V265" s="7" t="inlineStr"/>
       <c r="W265" s="6" t="inlineStr"/>
       <c r="X265" s="7" t="inlineStr"/>
@@ -23101,7 +23101,11 @@
       </c>
       <c r="N266" s="7" t="inlineStr"/>
       <c r="O266" s="6" t="inlineStr"/>
-      <c r="P266" s="7" t="inlineStr"/>
+      <c r="P266" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q266" s="6" t="inlineStr"/>
       <c r="R266" s="7" t="inlineStr"/>
       <c r="S266" s="6" t="inlineStr"/>
@@ -23110,11 +23114,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U266" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U266" s="6" t="inlineStr"/>
       <c r="V266" s="7" t="inlineStr"/>
       <c r="W266" s="6" t="inlineStr"/>
       <c r="X266" s="7" t="inlineStr"/>
@@ -23179,7 +23179,11 @@
       </c>
       <c r="N267" s="7" t="inlineStr"/>
       <c r="O267" s="6" t="inlineStr"/>
-      <c r="P267" s="7" t="inlineStr"/>
+      <c r="P267" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q267" s="6" t="inlineStr"/>
       <c r="R267" s="7" t="inlineStr"/>
       <c r="S267" s="6" t="inlineStr"/>
@@ -23188,11 +23192,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U267" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U267" s="6" t="inlineStr"/>
       <c r="V267" s="7" t="inlineStr"/>
       <c r="W267" s="6" t="inlineStr"/>
       <c r="X267" s="7" t="inlineStr"/>
@@ -23257,7 +23257,11 @@
       </c>
       <c r="N268" s="7" t="inlineStr"/>
       <c r="O268" s="6" t="inlineStr"/>
-      <c r="P268" s="7" t="inlineStr"/>
+      <c r="P268" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q268" s="6" t="inlineStr"/>
       <c r="R268" s="7" t="inlineStr"/>
       <c r="S268" s="6" t="inlineStr"/>
@@ -23266,11 +23270,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U268" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U268" s="6" t="inlineStr"/>
       <c r="V268" s="7" t="inlineStr"/>
       <c r="W268" s="6" t="inlineStr"/>
       <c r="X268" s="7" t="inlineStr"/>
@@ -23335,7 +23335,11 @@
       </c>
       <c r="N269" s="7" t="inlineStr"/>
       <c r="O269" s="6" t="inlineStr"/>
-      <c r="P269" s="7" t="inlineStr"/>
+      <c r="P269" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q269" s="6" t="inlineStr"/>
       <c r="R269" s="7" t="inlineStr"/>
       <c r="S269" s="6" t="inlineStr"/>
@@ -23344,11 +23348,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U269" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U269" s="6" t="inlineStr"/>
       <c r="V269" s="7" t="inlineStr"/>
       <c r="W269" s="6" t="inlineStr"/>
       <c r="X269" s="7" t="inlineStr"/>
@@ -23413,7 +23413,11 @@
       </c>
       <c r="N270" s="7" t="inlineStr"/>
       <c r="O270" s="6" t="inlineStr"/>
-      <c r="P270" s="7" t="inlineStr"/>
+      <c r="P270" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q270" s="6" t="inlineStr"/>
       <c r="R270" s="7" t="inlineStr"/>
       <c r="S270" s="6" t="inlineStr"/>
@@ -23422,11 +23426,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U270" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U270" s="6" t="inlineStr"/>
       <c r="V270" s="7" t="inlineStr"/>
       <c r="W270" s="6" t="inlineStr"/>
       <c r="X270" s="7" t="inlineStr"/>
@@ -23491,7 +23491,11 @@
       </c>
       <c r="N271" s="7" t="inlineStr"/>
       <c r="O271" s="6" t="inlineStr"/>
-      <c r="P271" s="7" t="inlineStr"/>
+      <c r="P271" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q271" s="6" t="inlineStr"/>
       <c r="R271" s="7" t="inlineStr"/>
       <c r="S271" s="6" t="inlineStr"/>
@@ -23500,11 +23504,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U271" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U271" s="6" t="inlineStr"/>
       <c r="V271" s="7" t="inlineStr"/>
       <c r="W271" s="6" t="inlineStr"/>
       <c r="X271" s="7" t="inlineStr"/>
@@ -23569,7 +23569,11 @@
       </c>
       <c r="N272" s="7" t="inlineStr"/>
       <c r="O272" s="6" t="inlineStr"/>
-      <c r="P272" s="7" t="inlineStr"/>
+      <c r="P272" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q272" s="6" t="inlineStr"/>
       <c r="R272" s="7" t="inlineStr"/>
       <c r="S272" s="6" t="inlineStr"/>
@@ -23578,11 +23582,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U272" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U272" s="6" t="inlineStr"/>
       <c r="V272" s="7" t="inlineStr"/>
       <c r="W272" s="6" t="inlineStr"/>
       <c r="X272" s="7" t="inlineStr"/>
@@ -23647,7 +23647,11 @@
       </c>
       <c r="N273" s="7" t="inlineStr"/>
       <c r="O273" s="6" t="inlineStr"/>
-      <c r="P273" s="7" t="inlineStr"/>
+      <c r="P273" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q273" s="6" t="inlineStr"/>
       <c r="R273" s="7" t="inlineStr"/>
       <c r="S273" s="6" t="inlineStr"/>
@@ -23656,11 +23660,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U273" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U273" s="6" t="inlineStr"/>
       <c r="V273" s="7" t="inlineStr"/>
       <c r="W273" s="6" t="inlineStr"/>
       <c r="X273" s="7" t="inlineStr"/>
@@ -23725,7 +23725,11 @@
       </c>
       <c r="N274" s="7" t="inlineStr"/>
       <c r="O274" s="6" t="inlineStr"/>
-      <c r="P274" s="7" t="inlineStr"/>
+      <c r="P274" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q274" s="6" t="inlineStr"/>
       <c r="R274" s="7" t="inlineStr"/>
       <c r="S274" s="6" t="inlineStr"/>
@@ -23734,11 +23738,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U274" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U274" s="6" t="inlineStr"/>
       <c r="V274" s="7" t="inlineStr"/>
       <c r="W274" s="6" t="inlineStr"/>
       <c r="X274" s="7" t="inlineStr"/>
@@ -23803,7 +23803,11 @@
       </c>
       <c r="N275" s="7" t="inlineStr"/>
       <c r="O275" s="6" t="inlineStr"/>
-      <c r="P275" s="7" t="inlineStr"/>
+      <c r="P275" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q275" s="6" t="inlineStr"/>
       <c r="R275" s="7" t="inlineStr"/>
       <c r="S275" s="6" t="inlineStr"/>
@@ -23812,11 +23816,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U275" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U275" s="6" t="inlineStr"/>
       <c r="V275" s="7" t="inlineStr"/>
       <c r="W275" s="6" t="inlineStr"/>
       <c r="X275" s="7" t="inlineStr"/>
@@ -23881,7 +23881,11 @@
       </c>
       <c r="N276" s="7" t="inlineStr"/>
       <c r="O276" s="6" t="inlineStr"/>
-      <c r="P276" s="7" t="inlineStr"/>
+      <c r="P276" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q276" s="6" t="inlineStr"/>
       <c r="R276" s="7" t="inlineStr"/>
       <c r="S276" s="6" t="inlineStr"/>
@@ -23890,11 +23894,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U276" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U276" s="6" t="inlineStr"/>
       <c r="V276" s="7" t="inlineStr"/>
       <c r="W276" s="6" t="inlineStr"/>
       <c r="X276" s="7" t="inlineStr"/>
@@ -23959,7 +23959,11 @@
       </c>
       <c r="N277" s="7" t="inlineStr"/>
       <c r="O277" s="6" t="inlineStr"/>
-      <c r="P277" s="7" t="inlineStr"/>
+      <c r="P277" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q277" s="6" t="inlineStr"/>
       <c r="R277" s="7" t="inlineStr"/>
       <c r="S277" s="6" t="inlineStr"/>
@@ -23968,11 +23972,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U277" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U277" s="6" t="inlineStr"/>
       <c r="V277" s="7" t="inlineStr"/>
       <c r="W277" s="6" t="inlineStr"/>
       <c r="X277" s="7" t="inlineStr"/>
@@ -24037,7 +24037,11 @@
       </c>
       <c r="N278" s="3" t="inlineStr"/>
       <c r="O278" s="2" t="inlineStr"/>
-      <c r="P278" s="3" t="inlineStr"/>
+      <c r="P278" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q278" s="2" t="inlineStr"/>
       <c r="R278" s="3" t="inlineStr"/>
       <c r="S278" s="2" t="inlineStr"/>
@@ -24046,11 +24050,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U278" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" s="3" t="inlineStr"/>
       <c r="W278" s="2" t="inlineStr"/>
       <c r="X278" s="3" t="inlineStr"/>
@@ -24123,7 +24123,11 @@
       </c>
       <c r="N279" s="7" t="inlineStr"/>
       <c r="O279" s="6" t="inlineStr"/>
-      <c r="P279" s="7" t="inlineStr"/>
+      <c r="P279" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q279" s="6" t="inlineStr"/>
       <c r="R279" s="7" t="inlineStr"/>
       <c r="S279" s="6" t="inlineStr"/>
@@ -24132,11 +24136,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U279" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U279" s="6" t="inlineStr"/>
       <c r="V279" s="7" t="inlineStr"/>
       <c r="W279" s="6" t="inlineStr"/>
       <c r="X279" s="7" t="inlineStr"/>
@@ -24209,7 +24209,11 @@
       </c>
       <c r="N280" s="7" t="inlineStr"/>
       <c r="O280" s="6" t="inlineStr"/>
-      <c r="P280" s="7" t="inlineStr"/>
+      <c r="P280" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q280" s="6" t="inlineStr"/>
       <c r="R280" s="7" t="inlineStr"/>
       <c r="S280" s="6" t="inlineStr"/>
@@ -24218,11 +24222,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U280" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U280" s="6" t="inlineStr"/>
       <c r="V280" s="7" t="inlineStr"/>
       <c r="W280" s="6" t="inlineStr"/>
       <c r="X280" s="7" t="inlineStr"/>
@@ -24295,7 +24295,11 @@
       </c>
       <c r="N281" s="7" t="inlineStr"/>
       <c r="O281" s="6" t="inlineStr"/>
-      <c r="P281" s="7" t="inlineStr"/>
+      <c r="P281" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q281" s="6" t="inlineStr"/>
       <c r="R281" s="7" t="inlineStr"/>
       <c r="S281" s="6" t="inlineStr"/>
@@ -24304,11 +24308,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U281" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U281" s="6" t="inlineStr"/>
       <c r="V281" s="7" t="inlineStr"/>
       <c r="W281" s="6" t="inlineStr"/>
       <c r="X281" s="7" t="inlineStr"/>
@@ -24381,7 +24381,11 @@
       </c>
       <c r="N282" s="3" t="inlineStr"/>
       <c r="O282" s="2" t="inlineStr"/>
-      <c r="P282" s="3" t="inlineStr"/>
+      <c r="P282" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q282" s="2" t="inlineStr"/>
       <c r="R282" s="3" t="inlineStr"/>
       <c r="S282" s="2" t="inlineStr"/>
@@ -24390,11 +24394,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U282" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" s="3" t="inlineStr"/>
       <c r="W282" s="2" t="inlineStr"/>
       <c r="X282" s="3" t="inlineStr"/>
@@ -24467,7 +24467,11 @@
       </c>
       <c r="N283" s="7" t="inlineStr"/>
       <c r="O283" s="6" t="inlineStr"/>
-      <c r="P283" s="7" t="inlineStr"/>
+      <c r="P283" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q283" s="6" t="inlineStr"/>
       <c r="R283" s="7" t="inlineStr"/>
       <c r="S283" s="6" t="inlineStr"/>
@@ -24476,11 +24480,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U283" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U283" s="6" t="inlineStr"/>
       <c r="V283" s="7" t="inlineStr"/>
       <c r="W283" s="6" t="inlineStr"/>
       <c r="X283" s="7" t="inlineStr"/>
@@ -24553,7 +24553,11 @@
       </c>
       <c r="N284" s="7" t="inlineStr"/>
       <c r="O284" s="6" t="inlineStr"/>
-      <c r="P284" s="7" t="inlineStr"/>
+      <c r="P284" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q284" s="6" t="inlineStr"/>
       <c r="R284" s="7" t="inlineStr"/>
       <c r="S284" s="6" t="inlineStr"/>
@@ -24562,11 +24566,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U284" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U284" s="6" t="inlineStr"/>
       <c r="V284" s="7" t="inlineStr"/>
       <c r="W284" s="6" t="inlineStr"/>
       <c r="X284" s="7" t="inlineStr"/>
@@ -24639,7 +24639,11 @@
       </c>
       <c r="N285" s="7" t="inlineStr"/>
       <c r="O285" s="6" t="inlineStr"/>
-      <c r="P285" s="7" t="inlineStr"/>
+      <c r="P285" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q285" s="6" t="inlineStr"/>
       <c r="R285" s="7" t="inlineStr"/>
       <c r="S285" s="6" t="inlineStr"/>
@@ -24648,11 +24652,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U285" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U285" s="6" t="inlineStr"/>
       <c r="V285" s="7" t="inlineStr"/>
       <c r="W285" s="6" t="inlineStr"/>
       <c r="X285" s="7" t="inlineStr"/>
@@ -24725,7 +24725,11 @@
       </c>
       <c r="N286" s="7" t="inlineStr"/>
       <c r="O286" s="6" t="inlineStr"/>
-      <c r="P286" s="7" t="inlineStr"/>
+      <c r="P286" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q286" s="6" t="inlineStr"/>
       <c r="R286" s="7" t="inlineStr"/>
       <c r="S286" s="6" t="inlineStr"/>
@@ -24734,11 +24738,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U286" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U286" s="6" t="inlineStr"/>
       <c r="V286" s="7" t="inlineStr"/>
       <c r="W286" s="6" t="inlineStr"/>
       <c r="X286" s="7" t="inlineStr"/>
@@ -24811,7 +24811,11 @@
       </c>
       <c r="N287" s="3" t="inlineStr"/>
       <c r="O287" s="2" t="inlineStr"/>
-      <c r="P287" s="3" t="inlineStr"/>
+      <c r="P287" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q287" s="2" t="inlineStr"/>
       <c r="R287" s="3" t="inlineStr"/>
       <c r="S287" s="2" t="inlineStr"/>
@@ -24820,11 +24824,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U287" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" s="3" t="inlineStr"/>
       <c r="W287" s="2" t="inlineStr"/>
       <c r="X287" s="3" t="inlineStr"/>
@@ -24897,7 +24897,11 @@
       </c>
       <c r="N288" s="7" t="inlineStr"/>
       <c r="O288" s="6" t="inlineStr"/>
-      <c r="P288" s="7" t="inlineStr"/>
+      <c r="P288" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q288" s="6" t="inlineStr"/>
       <c r="R288" s="7" t="inlineStr"/>
       <c r="S288" s="6" t="inlineStr"/>
@@ -24906,11 +24910,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U288" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U288" s="6" t="inlineStr"/>
       <c r="V288" s="7" t="inlineStr"/>
       <c r="W288" s="6" t="inlineStr"/>
       <c r="X288" s="7" t="inlineStr"/>
@@ -24983,7 +24983,11 @@
       </c>
       <c r="N289" s="7" t="inlineStr"/>
       <c r="O289" s="6" t="inlineStr"/>
-      <c r="P289" s="7" t="inlineStr"/>
+      <c r="P289" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q289" s="6" t="inlineStr"/>
       <c r="R289" s="7" t="inlineStr"/>
       <c r="S289" s="6" t="inlineStr"/>
@@ -24992,11 +24996,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U289" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U289" s="6" t="inlineStr"/>
       <c r="V289" s="7" t="inlineStr"/>
       <c r="W289" s="6" t="inlineStr"/>
       <c r="X289" s="7" t="inlineStr"/>
@@ -25069,7 +25069,11 @@
       </c>
       <c r="N290" s="7" t="inlineStr"/>
       <c r="O290" s="6" t="inlineStr"/>
-      <c r="P290" s="7" t="inlineStr"/>
+      <c r="P290" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q290" s="6" t="inlineStr"/>
       <c r="R290" s="7" t="inlineStr"/>
       <c r="S290" s="6" t="inlineStr"/>
@@ -25078,11 +25082,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U290" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U290" s="6" t="inlineStr"/>
       <c r="V290" s="7" t="inlineStr"/>
       <c r="W290" s="6" t="inlineStr"/>
       <c r="X290" s="7" t="inlineStr"/>
@@ -25155,7 +25155,11 @@
       </c>
       <c r="N291" s="3" t="inlineStr"/>
       <c r="O291" s="2" t="inlineStr"/>
-      <c r="P291" s="3" t="inlineStr"/>
+      <c r="P291" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q291" s="2" t="inlineStr"/>
       <c r="R291" s="3" t="inlineStr"/>
       <c r="S291" s="2" t="inlineStr"/>
@@ -25164,11 +25168,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U291" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
       <c r="V291" s="3" t="inlineStr"/>
       <c r="W291" s="2" t="inlineStr"/>
       <c r="X291" s="3" t="inlineStr"/>
@@ -25233,7 +25233,11 @@
       </c>
       <c r="N292" s="7" t="inlineStr"/>
       <c r="O292" s="6" t="inlineStr"/>
-      <c r="P292" s="7" t="inlineStr"/>
+      <c r="P292" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q292" s="6" t="inlineStr"/>
       <c r="R292" s="7" t="inlineStr"/>
       <c r="S292" s="6" t="inlineStr"/>
@@ -25242,11 +25246,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U292" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U292" s="6" t="inlineStr"/>
       <c r="V292" s="7" t="inlineStr"/>
       <c r="W292" s="6" t="inlineStr"/>
       <c r="X292" s="7" t="inlineStr"/>
@@ -25311,7 +25311,11 @@
       </c>
       <c r="N293" s="7" t="inlineStr"/>
       <c r="O293" s="6" t="inlineStr"/>
-      <c r="P293" s="7" t="inlineStr"/>
+      <c r="P293" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q293" s="6" t="inlineStr"/>
       <c r="R293" s="7" t="inlineStr"/>
       <c r="S293" s="6" t="inlineStr"/>
@@ -25320,11 +25324,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U293" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U293" s="6" t="inlineStr"/>
       <c r="V293" s="7" t="inlineStr"/>
       <c r="W293" s="6" t="inlineStr"/>
       <c r="X293" s="7" t="inlineStr"/>
@@ -25389,7 +25389,11 @@
       </c>
       <c r="N294" s="7" t="inlineStr"/>
       <c r="O294" s="6" t="inlineStr"/>
-      <c r="P294" s="7" t="inlineStr"/>
+      <c r="P294" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q294" s="6" t="inlineStr"/>
       <c r="R294" s="7" t="inlineStr"/>
       <c r="S294" s="6" t="inlineStr"/>
@@ -25398,11 +25402,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U294" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U294" s="6" t="inlineStr"/>
       <c r="V294" s="7" t="inlineStr"/>
       <c r="W294" s="6" t="inlineStr"/>
       <c r="X294" s="7" t="inlineStr"/>
@@ -25467,7 +25467,11 @@
       </c>
       <c r="N295" s="7" t="inlineStr"/>
       <c r="O295" s="6" t="inlineStr"/>
-      <c r="P295" s="7" t="inlineStr"/>
+      <c r="P295" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q295" s="6" t="inlineStr"/>
       <c r="R295" s="7" t="inlineStr"/>
       <c r="S295" s="6" t="inlineStr"/>
@@ -25476,11 +25480,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U295" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U295" s="6" t="inlineStr"/>
       <c r="V295" s="7" t="inlineStr"/>
       <c r="W295" s="6" t="inlineStr"/>
       <c r="X295" s="7" t="inlineStr"/>
@@ -25545,7 +25545,11 @@
       </c>
       <c r="N296" s="7" t="inlineStr"/>
       <c r="O296" s="6" t="inlineStr"/>
-      <c r="P296" s="7" t="inlineStr"/>
+      <c r="P296" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q296" s="6" t="inlineStr"/>
       <c r="R296" s="7" t="inlineStr"/>
       <c r="S296" s="6" t="inlineStr"/>
@@ -25554,11 +25558,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U296" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U296" s="6" t="inlineStr"/>
       <c r="V296" s="7" t="inlineStr"/>
       <c r="W296" s="6" t="inlineStr"/>
       <c r="X296" s="7" t="inlineStr"/>
@@ -25623,7 +25623,11 @@
       </c>
       <c r="N297" s="7" t="inlineStr"/>
       <c r="O297" s="6" t="inlineStr"/>
-      <c r="P297" s="7" t="inlineStr"/>
+      <c r="P297" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q297" s="6" t="inlineStr"/>
       <c r="R297" s="7" t="inlineStr"/>
       <c r="S297" s="6" t="inlineStr"/>
@@ -25632,11 +25636,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U297" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U297" s="6" t="inlineStr"/>
       <c r="V297" s="7" t="inlineStr"/>
       <c r="W297" s="6" t="inlineStr"/>
       <c r="X297" s="7" t="inlineStr"/>
@@ -25701,7 +25701,11 @@
       </c>
       <c r="N298" s="7" t="inlineStr"/>
       <c r="O298" s="6" t="inlineStr"/>
-      <c r="P298" s="7" t="inlineStr"/>
+      <c r="P298" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q298" s="6" t="inlineStr"/>
       <c r="R298" s="7" t="inlineStr"/>
       <c r="S298" s="6" t="inlineStr"/>
@@ -25710,11 +25714,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U298" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U298" s="6" t="inlineStr"/>
       <c r="V298" s="7" t="inlineStr"/>
       <c r="W298" s="6" t="inlineStr"/>
       <c r="X298" s="7" t="inlineStr"/>
@@ -25779,7 +25779,11 @@
       </c>
       <c r="N299" s="7" t="inlineStr"/>
       <c r="O299" s="6" t="inlineStr"/>
-      <c r="P299" s="7" t="inlineStr"/>
+      <c r="P299" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q299" s="6" t="inlineStr"/>
       <c r="R299" s="7" t="inlineStr"/>
       <c r="S299" s="6" t="inlineStr"/>
@@ -25788,11 +25792,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U299" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U299" s="6" t="inlineStr"/>
       <c r="V299" s="7" t="inlineStr"/>
       <c r="W299" s="6" t="inlineStr"/>
       <c r="X299" s="7" t="inlineStr"/>
@@ -25857,7 +25857,11 @@
       </c>
       <c r="N300" s="7" t="inlineStr"/>
       <c r="O300" s="6" t="inlineStr"/>
-      <c r="P300" s="7" t="inlineStr"/>
+      <c r="P300" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q300" s="6" t="inlineStr"/>
       <c r="R300" s="7" t="inlineStr"/>
       <c r="S300" s="6" t="inlineStr"/>
@@ -25866,11 +25870,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U300" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U300" s="6" t="inlineStr"/>
       <c r="V300" s="7" t="inlineStr"/>
       <c r="W300" s="6" t="inlineStr"/>
       <c r="X300" s="7" t="inlineStr"/>
@@ -25935,7 +25935,11 @@
       </c>
       <c r="N301" s="7" t="inlineStr"/>
       <c r="O301" s="6" t="inlineStr"/>
-      <c r="P301" s="7" t="inlineStr"/>
+      <c r="P301" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q301" s="6" t="inlineStr"/>
       <c r="R301" s="7" t="inlineStr"/>
       <c r="S301" s="6" t="inlineStr"/>
@@ -25944,11 +25948,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U301" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U301" s="6" t="inlineStr"/>
       <c r="V301" s="7" t="inlineStr"/>
       <c r="W301" s="6" t="inlineStr"/>
       <c r="X301" s="7" t="inlineStr"/>
@@ -26013,7 +26013,11 @@
       </c>
       <c r="N302" s="7" t="inlineStr"/>
       <c r="O302" s="6" t="inlineStr"/>
-      <c r="P302" s="7" t="inlineStr"/>
+      <c r="P302" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q302" s="6" t="inlineStr"/>
       <c r="R302" s="7" t="inlineStr"/>
       <c r="S302" s="6" t="inlineStr"/>
@@ -26022,11 +26026,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U302" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U302" s="6" t="inlineStr"/>
       <c r="V302" s="7" t="inlineStr"/>
       <c r="W302" s="6" t="inlineStr"/>
       <c r="X302" s="7" t="inlineStr"/>
@@ -26091,7 +26091,11 @@
       </c>
       <c r="N303" s="7" t="inlineStr"/>
       <c r="O303" s="6" t="inlineStr"/>
-      <c r="P303" s="7" t="inlineStr"/>
+      <c r="P303" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q303" s="6" t="inlineStr"/>
       <c r="R303" s="7" t="inlineStr"/>
       <c r="S303" s="6" t="inlineStr"/>
@@ -26100,11 +26104,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U303" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U303" s="6" t="inlineStr"/>
       <c r="V303" s="7" t="inlineStr"/>
       <c r="W303" s="6" t="inlineStr"/>
       <c r="X303" s="7" t="inlineStr"/>
@@ -26169,7 +26169,11 @@
       </c>
       <c r="N304" s="7" t="inlineStr"/>
       <c r="O304" s="6" t="inlineStr"/>
-      <c r="P304" s="7" t="inlineStr"/>
+      <c r="P304" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q304" s="6" t="inlineStr"/>
       <c r="R304" s="7" t="inlineStr"/>
       <c r="S304" s="6" t="inlineStr"/>
@@ -26178,11 +26182,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U304" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U304" s="6" t="inlineStr"/>
       <c r="V304" s="7" t="inlineStr"/>
       <c r="W304" s="6" t="inlineStr"/>
       <c r="X304" s="7" t="inlineStr"/>
@@ -26247,7 +26247,11 @@
       </c>
       <c r="N305" s="7" t="inlineStr"/>
       <c r="O305" s="6" t="inlineStr"/>
-      <c r="P305" s="7" t="inlineStr"/>
+      <c r="P305" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q305" s="6" t="inlineStr"/>
       <c r="R305" s="7" t="inlineStr"/>
       <c r="S305" s="6" t="inlineStr"/>
@@ -26256,11 +26260,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U305" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U305" s="6" t="inlineStr"/>
       <c r="V305" s="7" t="inlineStr"/>
       <c r="W305" s="6" t="inlineStr"/>
       <c r="X305" s="7" t="inlineStr"/>
@@ -26325,7 +26325,11 @@
       </c>
       <c r="N306" s="7" t="inlineStr"/>
       <c r="O306" s="6" t="inlineStr"/>
-      <c r="P306" s="7" t="inlineStr"/>
+      <c r="P306" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q306" s="6" t="inlineStr"/>
       <c r="R306" s="7" t="inlineStr"/>
       <c r="S306" s="6" t="inlineStr"/>
@@ -26334,11 +26338,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U306" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U306" s="6" t="inlineStr"/>
       <c r="V306" s="7" t="inlineStr"/>
       <c r="W306" s="6" t="inlineStr"/>
       <c r="X306" s="7" t="inlineStr"/>
@@ -26403,7 +26403,11 @@
       </c>
       <c r="N307" s="7" t="inlineStr"/>
       <c r="O307" s="6" t="inlineStr"/>
-      <c r="P307" s="7" t="inlineStr"/>
+      <c r="P307" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q307" s="6" t="inlineStr"/>
       <c r="R307" s="7" t="inlineStr"/>
       <c r="S307" s="6" t="inlineStr"/>
@@ -26412,11 +26416,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U307" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U307" s="6" t="inlineStr"/>
       <c r="V307" s="7" t="inlineStr"/>
       <c r="W307" s="6" t="inlineStr"/>
       <c r="X307" s="7" t="inlineStr"/>
@@ -26481,7 +26481,11 @@
       </c>
       <c r="N308" s="7" t="inlineStr"/>
       <c r="O308" s="6" t="inlineStr"/>
-      <c r="P308" s="7" t="inlineStr"/>
+      <c r="P308" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q308" s="6" t="inlineStr"/>
       <c r="R308" s="7" t="inlineStr"/>
       <c r="S308" s="6" t="inlineStr"/>
@@ -26490,11 +26494,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U308" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U308" s="6" t="inlineStr"/>
       <c r="V308" s="7" t="inlineStr"/>
       <c r="W308" s="6" t="inlineStr"/>
       <c r="X308" s="7" t="inlineStr"/>
@@ -26559,7 +26559,11 @@
       </c>
       <c r="N309" s="7" t="inlineStr"/>
       <c r="O309" s="6" t="inlineStr"/>
-      <c r="P309" s="7" t="inlineStr"/>
+      <c r="P309" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q309" s="6" t="inlineStr"/>
       <c r="R309" s="7" t="inlineStr"/>
       <c r="S309" s="6" t="inlineStr"/>
@@ -26568,11 +26572,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U309" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U309" s="6" t="inlineStr"/>
       <c r="V309" s="7" t="inlineStr"/>
       <c r="W309" s="6" t="inlineStr"/>
       <c r="X309" s="7" t="inlineStr"/>
@@ -26637,7 +26637,11 @@
       </c>
       <c r="N310" s="7" t="inlineStr"/>
       <c r="O310" s="6" t="inlineStr"/>
-      <c r="P310" s="7" t="inlineStr"/>
+      <c r="P310" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q310" s="6" t="inlineStr"/>
       <c r="R310" s="7" t="inlineStr"/>
       <c r="S310" s="6" t="inlineStr"/>
@@ -26646,11 +26650,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U310" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U310" s="6" t="inlineStr"/>
       <c r="V310" s="7" t="inlineStr"/>
       <c r="W310" s="6" t="inlineStr"/>
       <c r="X310" s="7" t="inlineStr"/>
@@ -26715,7 +26715,11 @@
       </c>
       <c r="N311" s="7" t="inlineStr"/>
       <c r="O311" s="6" t="inlineStr"/>
-      <c r="P311" s="7" t="inlineStr"/>
+      <c r="P311" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q311" s="6" t="inlineStr"/>
       <c r="R311" s="7" t="inlineStr"/>
       <c r="S311" s="6" t="inlineStr"/>
@@ -26724,11 +26728,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U311" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U311" s="6" t="inlineStr"/>
       <c r="V311" s="7" t="inlineStr"/>
       <c r="W311" s="6" t="inlineStr"/>
       <c r="X311" s="7" t="inlineStr"/>
@@ -26793,7 +26793,11 @@
       </c>
       <c r="N312" s="7" t="inlineStr"/>
       <c r="O312" s="6" t="inlineStr"/>
-      <c r="P312" s="7" t="inlineStr"/>
+      <c r="P312" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q312" s="6" t="inlineStr"/>
       <c r="R312" s="7" t="inlineStr"/>
       <c r="S312" s="6" t="inlineStr"/>
@@ -26802,11 +26806,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U312" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U312" s="6" t="inlineStr"/>
       <c r="V312" s="7" t="inlineStr"/>
       <c r="W312" s="6" t="inlineStr"/>
       <c r="X312" s="7" t="inlineStr"/>
@@ -26871,7 +26871,11 @@
       </c>
       <c r="N313" s="7" t="inlineStr"/>
       <c r="O313" s="6" t="inlineStr"/>
-      <c r="P313" s="7" t="inlineStr"/>
+      <c r="P313" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q313" s="6" t="inlineStr"/>
       <c r="R313" s="7" t="inlineStr"/>
       <c r="S313" s="6" t="inlineStr"/>
@@ -26880,11 +26884,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U313" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U313" s="6" t="inlineStr"/>
       <c r="V313" s="7" t="inlineStr"/>
       <c r="W313" s="6" t="inlineStr"/>
       <c r="X313" s="7" t="inlineStr"/>
@@ -26949,7 +26949,11 @@
       </c>
       <c r="N314" s="7" t="inlineStr"/>
       <c r="O314" s="6" t="inlineStr"/>
-      <c r="P314" s="7" t="inlineStr"/>
+      <c r="P314" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q314" s="6" t="inlineStr"/>
       <c r="R314" s="7" t="inlineStr"/>
       <c r="S314" s="6" t="inlineStr"/>
@@ -26958,11 +26962,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U314" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U314" s="6" t="inlineStr"/>
       <c r="V314" s="7" t="inlineStr"/>
       <c r="W314" s="6" t="inlineStr"/>
       <c r="X314" s="7" t="inlineStr"/>
@@ -27027,7 +27027,11 @@
       </c>
       <c r="N315" s="7" t="inlineStr"/>
       <c r="O315" s="6" t="inlineStr"/>
-      <c r="P315" s="7" t="inlineStr"/>
+      <c r="P315" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q315" s="6" t="inlineStr"/>
       <c r="R315" s="7" t="inlineStr"/>
       <c r="S315" s="6" t="inlineStr"/>
@@ -27036,11 +27040,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U315" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U315" s="6" t="inlineStr"/>
       <c r="V315" s="7" t="inlineStr"/>
       <c r="W315" s="6" t="inlineStr"/>
       <c r="X315" s="7" t="inlineStr"/>
@@ -27105,7 +27105,11 @@
       </c>
       <c r="N316" s="7" t="inlineStr"/>
       <c r="O316" s="6" t="inlineStr"/>
-      <c r="P316" s="7" t="inlineStr"/>
+      <c r="P316" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q316" s="6" t="inlineStr"/>
       <c r="R316" s="7" t="inlineStr"/>
       <c r="S316" s="6" t="inlineStr"/>
@@ -27114,11 +27118,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U316" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U316" s="6" t="inlineStr"/>
       <c r="V316" s="7" t="inlineStr"/>
       <c r="W316" s="6" t="inlineStr"/>
       <c r="X316" s="7" t="inlineStr"/>
@@ -27183,7 +27183,11 @@
       </c>
       <c r="N317" s="7" t="inlineStr"/>
       <c r="O317" s="6" t="inlineStr"/>
-      <c r="P317" s="7" t="inlineStr"/>
+      <c r="P317" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q317" s="6" t="inlineStr"/>
       <c r="R317" s="7" t="inlineStr"/>
       <c r="S317" s="6" t="inlineStr"/>
@@ -27192,11 +27196,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U317" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U317" s="6" t="inlineStr"/>
       <c r="V317" s="7" t="inlineStr"/>
       <c r="W317" s="6" t="inlineStr"/>
       <c r="X317" s="7" t="inlineStr"/>
@@ -27261,7 +27261,11 @@
       </c>
       <c r="N318" s="7" t="inlineStr"/>
       <c r="O318" s="6" t="inlineStr"/>
-      <c r="P318" s="7" t="inlineStr"/>
+      <c r="P318" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q318" s="6" t="inlineStr"/>
       <c r="R318" s="7" t="inlineStr"/>
       <c r="S318" s="6" t="inlineStr"/>
@@ -27270,11 +27274,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U318" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U318" s="6" t="inlineStr"/>
       <c r="V318" s="7" t="inlineStr"/>
       <c r="W318" s="6" t="inlineStr"/>
       <c r="X318" s="7" t="inlineStr"/>
@@ -27339,7 +27339,11 @@
       </c>
       <c r="N319" s="7" t="inlineStr"/>
       <c r="O319" s="6" t="inlineStr"/>
-      <c r="P319" s="7" t="inlineStr"/>
+      <c r="P319" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q319" s="6" t="inlineStr"/>
       <c r="R319" s="7" t="inlineStr"/>
       <c r="S319" s="6" t="inlineStr"/>
@@ -27348,11 +27352,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U319" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U319" s="6" t="inlineStr"/>
       <c r="V319" s="7" t="inlineStr"/>
       <c r="W319" s="6" t="inlineStr"/>
       <c r="X319" s="7" t="inlineStr"/>
@@ -27417,7 +27417,11 @@
       </c>
       <c r="N320" s="7" t="inlineStr"/>
       <c r="O320" s="6" t="inlineStr"/>
-      <c r="P320" s="7" t="inlineStr"/>
+      <c r="P320" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q320" s="6" t="inlineStr"/>
       <c r="R320" s="7" t="inlineStr"/>
       <c r="S320" s="6" t="inlineStr"/>
@@ -27426,11 +27430,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U320" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U320" s="6" t="inlineStr"/>
       <c r="V320" s="7" t="inlineStr"/>
       <c r="W320" s="6" t="inlineStr"/>
       <c r="X320" s="7" t="inlineStr"/>
@@ -27495,7 +27495,11 @@
       </c>
       <c r="N321" s="7" t="inlineStr"/>
       <c r="O321" s="6" t="inlineStr"/>
-      <c r="P321" s="7" t="inlineStr"/>
+      <c r="P321" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q321" s="6" t="inlineStr"/>
       <c r="R321" s="7" t="inlineStr"/>
       <c r="S321" s="6" t="inlineStr"/>
@@ -27504,11 +27508,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U321" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U321" s="6" t="inlineStr"/>
       <c r="V321" s="7" t="inlineStr"/>
       <c r="W321" s="6" t="inlineStr"/>
       <c r="X321" s="7" t="inlineStr"/>
@@ -27573,7 +27573,11 @@
       </c>
       <c r="N322" s="7" t="inlineStr"/>
       <c r="O322" s="6" t="inlineStr"/>
-      <c r="P322" s="7" t="inlineStr"/>
+      <c r="P322" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q322" s="6" t="inlineStr"/>
       <c r="R322" s="7" t="inlineStr"/>
       <c r="S322" s="6" t="inlineStr"/>
@@ -27582,11 +27586,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U322" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U322" s="6" t="inlineStr"/>
       <c r="V322" s="7" t="inlineStr"/>
       <c r="W322" s="6" t="inlineStr"/>
       <c r="X322" s="7" t="inlineStr"/>
@@ -27651,7 +27651,11 @@
       </c>
       <c r="N323" s="7" t="inlineStr"/>
       <c r="O323" s="6" t="inlineStr"/>
-      <c r="P323" s="7" t="inlineStr"/>
+      <c r="P323" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q323" s="6" t="inlineStr"/>
       <c r="R323" s="7" t="inlineStr"/>
       <c r="S323" s="6" t="inlineStr"/>
@@ -27660,11 +27664,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U323" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U323" s="6" t="inlineStr"/>
       <c r="V323" s="7" t="inlineStr"/>
       <c r="W323" s="6" t="inlineStr"/>
       <c r="X323" s="7" t="inlineStr"/>
@@ -27729,7 +27729,11 @@
       </c>
       <c r="N324" s="7" t="inlineStr"/>
       <c r="O324" s="6" t="inlineStr"/>
-      <c r="P324" s="7" t="inlineStr"/>
+      <c r="P324" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q324" s="6" t="inlineStr"/>
       <c r="R324" s="7" t="inlineStr"/>
       <c r="S324" s="6" t="inlineStr"/>
@@ -27738,11 +27742,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U324" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U324" s="6" t="inlineStr"/>
       <c r="V324" s="7" t="inlineStr"/>
       <c r="W324" s="6" t="inlineStr"/>
       <c r="X324" s="7" t="inlineStr"/>
@@ -27807,16 +27807,16 @@
       </c>
       <c r="N325" s="7" t="inlineStr"/>
       <c r="O325" s="6" t="inlineStr"/>
-      <c r="P325" s="7" t="inlineStr"/>
+      <c r="P325" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q325" s="6" t="inlineStr"/>
       <c r="R325" s="7" t="inlineStr"/>
       <c r="S325" s="6" t="inlineStr"/>
       <c r="T325" s="7" t="inlineStr"/>
-      <c r="U325" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U325" s="6" t="inlineStr"/>
       <c r="V325" s="7" t="inlineStr"/>
       <c r="W325" s="6" t="inlineStr"/>
       <c r="X325" s="7" t="inlineStr"/>
@@ -27885,16 +27885,16 @@
       </c>
       <c r="N326" s="7" t="inlineStr"/>
       <c r="O326" s="6" t="inlineStr"/>
-      <c r="P326" s="7" t="inlineStr"/>
+      <c r="P326" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q326" s="6" t="inlineStr"/>
       <c r="R326" s="7" t="inlineStr"/>
       <c r="S326" s="6" t="inlineStr"/>
       <c r="T326" s="7" t="inlineStr"/>
-      <c r="U326" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U326" s="6" t="inlineStr"/>
       <c r="V326" s="7" t="inlineStr"/>
       <c r="W326" s="6" t="inlineStr"/>
       <c r="X326" s="7" t="inlineStr"/>
@@ -27963,7 +27963,11 @@
       </c>
       <c r="N327" s="7" t="inlineStr"/>
       <c r="O327" s="6" t="inlineStr"/>
-      <c r="P327" s="7" t="inlineStr"/>
+      <c r="P327" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Q327" s="6" t="inlineStr"/>
       <c r="R327" s="7" t="inlineStr"/>
       <c r="S327" s="6" t="inlineStr"/>
@@ -27972,11 +27976,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U327" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="U327" s="6" t="inlineStr"/>
       <c r="V327" s="7" t="inlineStr"/>
       <c r="W327" s="6" t="inlineStr"/>
       <c r="X327" s="7" t="inlineStr"/>
@@ -28045,7 +28045,11 @@
       </c>
       <c r="N328" s="3" t="inlineStr"/>
       <c r="O328" s="2" t="inlineStr"/>
-      <c r="P328" s="3" t="inlineStr"/>
+      <c r="P328" s="4" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q328" s="2" t="inlineStr"/>
       <c r="R328" s="3" t="inlineStr"/>
       <c r="S328" s="2" t="inlineStr"/>
@@ -28054,11 +28058,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U328" s="9" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" s="3" t="inlineStr"/>
       <c r="W328" s="2" t="inlineStr"/>
       <c r="X328" s="3" t="inlineStr"/>
@@ -28123,7 +28123,11 @@
       </c>
       <c r="N329" s="7" t="inlineStr"/>
       <c r="O329" s="6" t="inlineStr"/>
-      <c r="P329" s="7" t="inlineStr"/>
+      <c r="P329" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q329" s="6" t="inlineStr"/>
       <c r="R329" s="7" t="inlineStr"/>
       <c r="S329" s="6" t="inlineStr"/>
@@ -28132,11 +28136,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U329" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U329" s="6" t="inlineStr"/>
       <c r="V329" s="7" t="inlineStr"/>
       <c r="W329" s="6" t="inlineStr"/>
       <c r="X329" s="7" t="inlineStr"/>
@@ -28201,7 +28201,11 @@
       </c>
       <c r="N330" s="7" t="inlineStr"/>
       <c r="O330" s="6" t="inlineStr"/>
-      <c r="P330" s="7" t="inlineStr"/>
+      <c r="P330" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q330" s="6" t="inlineStr"/>
       <c r="R330" s="7" t="inlineStr"/>
       <c r="S330" s="6" t="inlineStr"/>
@@ -28210,11 +28214,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U330" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U330" s="6" t="inlineStr"/>
       <c r="V330" s="7" t="inlineStr"/>
       <c r="W330" s="6" t="inlineStr"/>
       <c r="X330" s="7" t="inlineStr"/>
@@ -28279,7 +28279,11 @@
       </c>
       <c r="N331" s="7" t="inlineStr"/>
       <c r="O331" s="6" t="inlineStr"/>
-      <c r="P331" s="7" t="inlineStr"/>
+      <c r="P331" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q331" s="6" t="inlineStr"/>
       <c r="R331" s="7" t="inlineStr"/>
       <c r="S331" s="6" t="inlineStr"/>
@@ -28288,11 +28292,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U331" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U331" s="6" t="inlineStr"/>
       <c r="V331" s="7" t="inlineStr"/>
       <c r="W331" s="6" t="inlineStr"/>
       <c r="X331" s="7" t="inlineStr"/>
@@ -28357,7 +28357,11 @@
       </c>
       <c r="N332" s="7" t="inlineStr"/>
       <c r="O332" s="6" t="inlineStr"/>
-      <c r="P332" s="7" t="inlineStr"/>
+      <c r="P332" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q332" s="6" t="inlineStr"/>
       <c r="R332" s="7" t="inlineStr"/>
       <c r="S332" s="6" t="inlineStr"/>
@@ -28366,11 +28370,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U332" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U332" s="6" t="inlineStr"/>
       <c r="V332" s="7" t="inlineStr"/>
       <c r="W332" s="6" t="inlineStr"/>
       <c r="X332" s="7" t="inlineStr"/>
@@ -28443,7 +28443,11 @@
       </c>
       <c r="N333" s="7" t="inlineStr"/>
       <c r="O333" s="6" t="inlineStr"/>
-      <c r="P333" s="7" t="inlineStr"/>
+      <c r="P333" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q333" s="6" t="inlineStr"/>
       <c r="R333" s="7" t="inlineStr"/>
       <c r="S333" s="6" t="inlineStr"/>
@@ -28452,11 +28456,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U333" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U333" s="6" t="inlineStr"/>
       <c r="V333" s="7" t="inlineStr"/>
       <c r="W333" s="6" t="inlineStr"/>
       <c r="X333" s="7" t="inlineStr"/>
@@ -28529,7 +28529,11 @@
       </c>
       <c r="N334" s="7" t="inlineStr"/>
       <c r="O334" s="6" t="inlineStr"/>
-      <c r="P334" s="7" t="inlineStr"/>
+      <c r="P334" s="8" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q334" s="6" t="inlineStr"/>
       <c r="R334" s="7" t="inlineStr"/>
       <c r="S334" s="6" t="inlineStr"/>
@@ -28538,11 +28542,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U334" s="10" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U334" s="6" t="inlineStr"/>
       <c r="V334" s="7" t="inlineStr"/>
       <c r="W334" s="6" t="inlineStr"/>
       <c r="X334" s="7" t="inlineStr"/>
@@ -28613,13 +28613,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N335" s="3" t="inlineStr"/>
+      <c r="N335" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O335" s="2" t="inlineStr"/>
-      <c r="P335" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P335" s="3" t="inlineStr"/>
       <c r="Q335" s="2" t="inlineStr"/>
       <c r="R335" s="3" t="inlineStr">
         <is>
@@ -28699,13 +28699,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N336" s="7" t="inlineStr"/>
+      <c r="N336" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O336" s="6" t="inlineStr"/>
-      <c r="P336" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P336" s="7" t="inlineStr"/>
       <c r="Q336" s="6" t="inlineStr"/>
       <c r="R336" s="7" t="inlineStr">
         <is>
@@ -28785,13 +28785,13 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N337" s="7" t="inlineStr"/>
+      <c r="N337" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="O337" s="6" t="inlineStr"/>
-      <c r="P337" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="P337" s="7" t="inlineStr"/>
       <c r="Q337" s="6" t="inlineStr"/>
       <c r="R337" s="7" t="inlineStr">
         <is>
@@ -28871,11 +28871,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N338" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N338" s="3" t="inlineStr"/>
       <c r="O338" s="2" t="inlineStr"/>
       <c r="P338" s="3" t="inlineStr"/>
       <c r="Q338" s="2" t="inlineStr"/>
@@ -28893,7 +28889,11 @@
       <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" s="3" t="inlineStr"/>
       <c r="W338" s="2" t="inlineStr"/>
-      <c r="X338" s="3" t="inlineStr"/>
+      <c r="X338" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y338" s="2" t="inlineStr"/>
       <c r="Z338" s="3" t="inlineStr"/>
       <c r="AA338" s="2" t="inlineStr"/>
@@ -28957,11 +28957,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N339" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N339" s="7" t="inlineStr"/>
       <c r="O339" s="6" t="inlineStr"/>
       <c r="P339" s="7" t="inlineStr"/>
       <c r="Q339" s="6" t="inlineStr"/>
@@ -28979,7 +28975,11 @@
       <c r="U339" s="6" t="inlineStr"/>
       <c r="V339" s="7" t="inlineStr"/>
       <c r="W339" s="6" t="inlineStr"/>
-      <c r="X339" s="7" t="inlineStr"/>
+      <c r="X339" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y339" s="6" t="inlineStr"/>
       <c r="Z339" s="7" t="inlineStr"/>
       <c r="AA339" s="6" t="inlineStr"/>
@@ -29043,11 +29043,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N340" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N340" s="7" t="inlineStr"/>
       <c r="O340" s="6" t="inlineStr"/>
       <c r="P340" s="7" t="inlineStr"/>
       <c r="Q340" s="6" t="inlineStr"/>
@@ -29065,7 +29061,11 @@
       <c r="U340" s="6" t="inlineStr"/>
       <c r="V340" s="7" t="inlineStr"/>
       <c r="W340" s="6" t="inlineStr"/>
-      <c r="X340" s="7" t="inlineStr"/>
+      <c r="X340" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y340" s="6" t="inlineStr"/>
       <c r="Z340" s="7" t="inlineStr"/>
       <c r="AA340" s="6" t="inlineStr"/>
@@ -29130,11 +29130,7 @@
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr"/>
-      <c r="O341" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O341" s="2" t="inlineStr"/>
       <c r="P341" s="3" t="inlineStr"/>
       <c r="Q341" s="2" t="inlineStr"/>
       <c r="R341" s="3" t="inlineStr">
@@ -29152,7 +29148,11 @@
       <c r="V341" s="3" t="inlineStr"/>
       <c r="W341" s="2" t="inlineStr"/>
       <c r="X341" s="3" t="inlineStr"/>
-      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Y341" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z341" s="3" t="inlineStr"/>
       <c r="AA341" s="2" t="inlineStr"/>
       <c r="AB341" s="2" t="inlineStr"/>
@@ -29216,11 +29216,7 @@
         </is>
       </c>
       <c r="N342" s="7" t="inlineStr"/>
-      <c r="O342" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O342" s="6" t="inlineStr"/>
       <c r="P342" s="7" t="inlineStr"/>
       <c r="Q342" s="6" t="inlineStr"/>
       <c r="R342" s="7" t="inlineStr">
@@ -29238,7 +29234,11 @@
       <c r="V342" s="7" t="inlineStr"/>
       <c r="W342" s="6" t="inlineStr"/>
       <c r="X342" s="7" t="inlineStr"/>
-      <c r="Y342" s="6" t="inlineStr"/>
+      <c r="Y342" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z342" s="7" t="inlineStr"/>
       <c r="AA342" s="6" t="inlineStr"/>
       <c r="AB342" s="6" t="inlineStr"/>
@@ -29302,11 +29302,7 @@
         </is>
       </c>
       <c r="N343" s="7" t="inlineStr"/>
-      <c r="O343" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O343" s="6" t="inlineStr"/>
       <c r="P343" s="7" t="inlineStr"/>
       <c r="Q343" s="6" t="inlineStr"/>
       <c r="R343" s="7" t="inlineStr">
@@ -29324,7 +29320,11 @@
       <c r="V343" s="7" t="inlineStr"/>
       <c r="W343" s="6" t="inlineStr"/>
       <c r="X343" s="7" t="inlineStr"/>
-      <c r="Y343" s="6" t="inlineStr"/>
+      <c r="Y343" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z343" s="7" t="inlineStr"/>
       <c r="AA343" s="6" t="inlineStr"/>
       <c r="AB343" s="6" t="inlineStr"/>
@@ -29390,7 +29390,11 @@
       <c r="N344" s="3" t="inlineStr"/>
       <c r="O344" s="2" t="inlineStr"/>
       <c r="P344" s="3" t="inlineStr"/>
-      <c r="Q344" s="2" t="inlineStr"/>
+      <c r="Q344" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R344" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -29407,11 +29411,7 @@
       <c r="W344" s="2" t="inlineStr"/>
       <c r="X344" s="3" t="inlineStr"/>
       <c r="Y344" s="2" t="inlineStr"/>
-      <c r="Z344" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z344" s="3" t="inlineStr"/>
       <c r="AA344" s="2" t="inlineStr"/>
       <c r="AB344" s="2" t="inlineStr"/>
       <c r="AC344" s="2" t="inlineStr">
@@ -29476,7 +29476,11 @@
       <c r="N345" s="7" t="inlineStr"/>
       <c r="O345" s="6" t="inlineStr"/>
       <c r="P345" s="7" t="inlineStr"/>
-      <c r="Q345" s="6" t="inlineStr"/>
+      <c r="Q345" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R345" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -29493,11 +29497,7 @@
       <c r="W345" s="6" t="inlineStr"/>
       <c r="X345" s="7" t="inlineStr"/>
       <c r="Y345" s="6" t="inlineStr"/>
-      <c r="Z345" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z345" s="7" t="inlineStr"/>
       <c r="AA345" s="6" t="inlineStr"/>
       <c r="AB345" s="6" t="inlineStr"/>
       <c r="AC345" s="6" t="inlineStr">
@@ -29562,7 +29562,11 @@
       <c r="N346" s="7" t="inlineStr"/>
       <c r="O346" s="6" t="inlineStr"/>
       <c r="P346" s="7" t="inlineStr"/>
-      <c r="Q346" s="6" t="inlineStr"/>
+      <c r="Q346" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R346" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -29579,11 +29583,7 @@
       <c r="W346" s="6" t="inlineStr"/>
       <c r="X346" s="7" t="inlineStr"/>
       <c r="Y346" s="6" t="inlineStr"/>
-      <c r="Z346" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z346" s="7" t="inlineStr"/>
       <c r="AA346" s="6" t="inlineStr"/>
       <c r="AB346" s="6" t="inlineStr"/>
       <c r="AC346" s="6" t="inlineStr">
@@ -30152,7 +30152,11 @@
       <c r="N353" s="3" t="inlineStr"/>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="3" t="inlineStr"/>
-      <c r="Q353" s="2" t="inlineStr"/>
+      <c r="Q353" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R353" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -30169,11 +30173,7 @@
       <c r="W353" s="2" t="inlineStr"/>
       <c r="X353" s="3" t="inlineStr"/>
       <c r="Y353" s="2" t="inlineStr"/>
-      <c r="Z353" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z353" s="3" t="inlineStr"/>
       <c r="AA353" s="2" t="inlineStr"/>
       <c r="AB353" s="2" t="inlineStr"/>
       <c r="AC353" s="2" t="inlineStr">
@@ -30242,7 +30242,11 @@
       <c r="N354" s="7" t="inlineStr"/>
       <c r="O354" s="6" t="inlineStr"/>
       <c r="P354" s="7" t="inlineStr"/>
-      <c r="Q354" s="6" t="inlineStr"/>
+      <c r="Q354" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R354" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30259,11 +30263,7 @@
       <c r="W354" s="6" t="inlineStr"/>
       <c r="X354" s="7" t="inlineStr"/>
       <c r="Y354" s="6" t="inlineStr"/>
-      <c r="Z354" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z354" s="7" t="inlineStr"/>
       <c r="AA354" s="6" t="inlineStr"/>
       <c r="AB354" s="6" t="inlineStr"/>
       <c r="AC354" s="6" t="inlineStr">
@@ -30332,7 +30332,11 @@
       <c r="N355" s="7" t="inlineStr"/>
       <c r="O355" s="6" t="inlineStr"/>
       <c r="P355" s="7" t="inlineStr"/>
-      <c r="Q355" s="6" t="inlineStr"/>
+      <c r="Q355" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R355" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30349,11 +30353,7 @@
       <c r="W355" s="6" t="inlineStr"/>
       <c r="X355" s="7" t="inlineStr"/>
       <c r="Y355" s="6" t="inlineStr"/>
-      <c r="Z355" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z355" s="7" t="inlineStr"/>
       <c r="AA355" s="6" t="inlineStr"/>
       <c r="AB355" s="6" t="inlineStr"/>
       <c r="AC355" s="6" t="inlineStr">
@@ -30422,7 +30422,11 @@
       <c r="N356" s="7" t="inlineStr"/>
       <c r="O356" s="6" t="inlineStr"/>
       <c r="P356" s="7" t="inlineStr"/>
-      <c r="Q356" s="6" t="inlineStr"/>
+      <c r="Q356" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R356" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30439,11 +30443,7 @@
       <c r="W356" s="6" t="inlineStr"/>
       <c r="X356" s="7" t="inlineStr"/>
       <c r="Y356" s="6" t="inlineStr"/>
-      <c r="Z356" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z356" s="7" t="inlineStr"/>
       <c r="AA356" s="6" t="inlineStr"/>
       <c r="AB356" s="6" t="inlineStr"/>
       <c r="AC356" s="6" t="inlineStr">
@@ -30512,7 +30512,11 @@
       <c r="N357" s="7" t="inlineStr"/>
       <c r="O357" s="6" t="inlineStr"/>
       <c r="P357" s="7" t="inlineStr"/>
-      <c r="Q357" s="6" t="inlineStr"/>
+      <c r="Q357" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R357" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30529,11 +30533,7 @@
       <c r="W357" s="6" t="inlineStr"/>
       <c r="X357" s="7" t="inlineStr"/>
       <c r="Y357" s="6" t="inlineStr"/>
-      <c r="Z357" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z357" s="7" t="inlineStr"/>
       <c r="AA357" s="6" t="inlineStr"/>
       <c r="AB357" s="6" t="inlineStr"/>
       <c r="AC357" s="6" t="inlineStr">
@@ -30602,7 +30602,11 @@
       <c r="N358" s="7" t="inlineStr"/>
       <c r="O358" s="6" t="inlineStr"/>
       <c r="P358" s="7" t="inlineStr"/>
-      <c r="Q358" s="6" t="inlineStr"/>
+      <c r="Q358" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R358" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30619,11 +30623,7 @@
       <c r="W358" s="6" t="inlineStr"/>
       <c r="X358" s="7" t="inlineStr"/>
       <c r="Y358" s="6" t="inlineStr"/>
-      <c r="Z358" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z358" s="7" t="inlineStr"/>
       <c r="AA358" s="6" t="inlineStr"/>
       <c r="AB358" s="6" t="inlineStr"/>
       <c r="AC358" s="6" t="inlineStr">
@@ -30692,7 +30692,11 @@
       <c r="N359" s="3" t="inlineStr"/>
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="3" t="inlineStr"/>
-      <c r="Q359" s="2" t="inlineStr"/>
+      <c r="Q359" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R359" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -30709,11 +30713,7 @@
       <c r="W359" s="2" t="inlineStr"/>
       <c r="X359" s="3" t="inlineStr"/>
       <c r="Y359" s="2" t="inlineStr"/>
-      <c r="Z359" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z359" s="3" t="inlineStr"/>
       <c r="AA359" s="2" t="inlineStr"/>
       <c r="AB359" s="2" t="inlineStr"/>
       <c r="AC359" s="2" t="inlineStr">
@@ -30782,7 +30782,11 @@
       <c r="N360" s="7" t="inlineStr"/>
       <c r="O360" s="6" t="inlineStr"/>
       <c r="P360" s="7" t="inlineStr"/>
-      <c r="Q360" s="6" t="inlineStr"/>
+      <c r="Q360" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R360" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30799,11 +30803,7 @@
       <c r="W360" s="6" t="inlineStr"/>
       <c r="X360" s="7" t="inlineStr"/>
       <c r="Y360" s="6" t="inlineStr"/>
-      <c r="Z360" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z360" s="7" t="inlineStr"/>
       <c r="AA360" s="6" t="inlineStr"/>
       <c r="AB360" s="6" t="inlineStr"/>
       <c r="AC360" s="6" t="inlineStr">
@@ -30872,7 +30872,11 @@
       <c r="N361" s="7" t="inlineStr"/>
       <c r="O361" s="6" t="inlineStr"/>
       <c r="P361" s="7" t="inlineStr"/>
-      <c r="Q361" s="6" t="inlineStr"/>
+      <c r="Q361" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R361" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30889,11 +30893,7 @@
       <c r="W361" s="6" t="inlineStr"/>
       <c r="X361" s="7" t="inlineStr"/>
       <c r="Y361" s="6" t="inlineStr"/>
-      <c r="Z361" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z361" s="7" t="inlineStr"/>
       <c r="AA361" s="6" t="inlineStr"/>
       <c r="AB361" s="6" t="inlineStr"/>
       <c r="AC361" s="6" t="inlineStr">
@@ -30962,7 +30962,11 @@
       <c r="N362" s="7" t="inlineStr"/>
       <c r="O362" s="6" t="inlineStr"/>
       <c r="P362" s="7" t="inlineStr"/>
-      <c r="Q362" s="6" t="inlineStr"/>
+      <c r="Q362" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R362" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -30979,11 +30983,7 @@
       <c r="W362" s="6" t="inlineStr"/>
       <c r="X362" s="7" t="inlineStr"/>
       <c r="Y362" s="6" t="inlineStr"/>
-      <c r="Z362" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z362" s="7" t="inlineStr"/>
       <c r="AA362" s="6" t="inlineStr"/>
       <c r="AB362" s="6" t="inlineStr"/>
       <c r="AC362" s="6" t="inlineStr">
@@ -31052,7 +31052,11 @@
       <c r="N363" s="7" t="inlineStr"/>
       <c r="O363" s="6" t="inlineStr"/>
       <c r="P363" s="7" t="inlineStr"/>
-      <c r="Q363" s="6" t="inlineStr"/>
+      <c r="Q363" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R363" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -31069,11 +31073,7 @@
       <c r="W363" s="6" t="inlineStr"/>
       <c r="X363" s="7" t="inlineStr"/>
       <c r="Y363" s="6" t="inlineStr"/>
-      <c r="Z363" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z363" s="7" t="inlineStr"/>
       <c r="AA363" s="6" t="inlineStr"/>
       <c r="AB363" s="6" t="inlineStr"/>
       <c r="AC363" s="6" t="inlineStr">
@@ -31142,7 +31142,11 @@
       <c r="N364" s="7" t="inlineStr"/>
       <c r="O364" s="6" t="inlineStr"/>
       <c r="P364" s="7" t="inlineStr"/>
-      <c r="Q364" s="6" t="inlineStr"/>
+      <c r="Q364" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R364" s="7" t="inlineStr">
         <is>
           <t>r</t>
@@ -31159,11 +31163,7 @@
       <c r="W364" s="6" t="inlineStr"/>
       <c r="X364" s="7" t="inlineStr"/>
       <c r="Y364" s="6" t="inlineStr"/>
-      <c r="Z364" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z364" s="7" t="inlineStr"/>
       <c r="AA364" s="6" t="inlineStr"/>
       <c r="AB364" s="6" t="inlineStr"/>
       <c r="AC364" s="6" t="inlineStr">
@@ -31229,11 +31229,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N365" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N365" s="3" t="inlineStr"/>
       <c r="O365" s="2" t="inlineStr"/>
       <c r="P365" s="3" t="inlineStr"/>
       <c r="Q365" s="2" t="inlineStr"/>
@@ -31251,7 +31247,11 @@
       <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" s="3" t="inlineStr"/>
       <c r="W365" s="2" t="inlineStr"/>
-      <c r="X365" s="3" t="inlineStr"/>
+      <c r="X365" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y365" s="2" t="inlineStr"/>
       <c r="Z365" s="3" t="inlineStr"/>
       <c r="AA365" s="2" t="inlineStr"/>
@@ -31319,11 +31319,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N366" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N366" s="7" t="inlineStr"/>
       <c r="O366" s="6" t="inlineStr"/>
       <c r="P366" s="7" t="inlineStr"/>
       <c r="Q366" s="6" t="inlineStr"/>
@@ -31341,7 +31337,11 @@
       <c r="U366" s="6" t="inlineStr"/>
       <c r="V366" s="7" t="inlineStr"/>
       <c r="W366" s="6" t="inlineStr"/>
-      <c r="X366" s="7" t="inlineStr"/>
+      <c r="X366" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y366" s="6" t="inlineStr"/>
       <c r="Z366" s="7" t="inlineStr"/>
       <c r="AA366" s="6" t="inlineStr"/>
@@ -31409,11 +31409,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N367" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N367" s="7" t="inlineStr"/>
       <c r="O367" s="6" t="inlineStr"/>
       <c r="P367" s="7" t="inlineStr"/>
       <c r="Q367" s="6" t="inlineStr"/>
@@ -31431,7 +31427,11 @@
       <c r="U367" s="6" t="inlineStr"/>
       <c r="V367" s="7" t="inlineStr"/>
       <c r="W367" s="6" t="inlineStr"/>
-      <c r="X367" s="7" t="inlineStr"/>
+      <c r="X367" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y367" s="6" t="inlineStr"/>
       <c r="Z367" s="7" t="inlineStr"/>
       <c r="AA367" s="6" t="inlineStr"/>
@@ -31499,11 +31499,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N368" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N368" s="7" t="inlineStr"/>
       <c r="O368" s="6" t="inlineStr"/>
       <c r="P368" s="7" t="inlineStr"/>
       <c r="Q368" s="6" t="inlineStr"/>
@@ -31521,7 +31517,11 @@
       <c r="U368" s="6" t="inlineStr"/>
       <c r="V368" s="7" t="inlineStr"/>
       <c r="W368" s="6" t="inlineStr"/>
-      <c r="X368" s="7" t="inlineStr"/>
+      <c r="X368" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y368" s="6" t="inlineStr"/>
       <c r="Z368" s="7" t="inlineStr"/>
       <c r="AA368" s="6" t="inlineStr"/>
@@ -31589,11 +31589,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N369" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N369" s="7" t="inlineStr"/>
       <c r="O369" s="6" t="inlineStr"/>
       <c r="P369" s="7" t="inlineStr"/>
       <c r="Q369" s="6" t="inlineStr"/>
@@ -31611,7 +31607,11 @@
       <c r="U369" s="6" t="inlineStr"/>
       <c r="V369" s="7" t="inlineStr"/>
       <c r="W369" s="6" t="inlineStr"/>
-      <c r="X369" s="7" t="inlineStr"/>
+      <c r="X369" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y369" s="6" t="inlineStr"/>
       <c r="Z369" s="7" t="inlineStr"/>
       <c r="AA369" s="6" t="inlineStr"/>
@@ -31679,11 +31679,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="N370" s="8" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="N370" s="7" t="inlineStr"/>
       <c r="O370" s="6" t="inlineStr"/>
       <c r="P370" s="7" t="inlineStr"/>
       <c r="Q370" s="6" t="inlineStr"/>
@@ -31701,7 +31697,11 @@
       <c r="U370" s="6" t="inlineStr"/>
       <c r="V370" s="7" t="inlineStr"/>
       <c r="W370" s="6" t="inlineStr"/>
-      <c r="X370" s="7" t="inlineStr"/>
+      <c r="X370" s="8" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Y370" s="6" t="inlineStr"/>
       <c r="Z370" s="7" t="inlineStr"/>
       <c r="AA370" s="6" t="inlineStr"/>
@@ -31770,11 +31770,7 @@
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr"/>
-      <c r="O371" s="9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O371" s="2" t="inlineStr"/>
       <c r="P371" s="3" t="inlineStr"/>
       <c r="Q371" s="2" t="inlineStr"/>
       <c r="R371" s="3" t="inlineStr">
@@ -31792,7 +31788,11 @@
       <c r="V371" s="3" t="inlineStr"/>
       <c r="W371" s="2" t="inlineStr"/>
       <c r="X371" s="3" t="inlineStr"/>
-      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Y371" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z371" s="3" t="inlineStr"/>
       <c r="AA371" s="2" t="inlineStr"/>
       <c r="AB371" s="2" t="inlineStr"/>
@@ -31860,11 +31860,7 @@
         </is>
       </c>
       <c r="N372" s="7" t="inlineStr"/>
-      <c r="O372" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O372" s="6" t="inlineStr"/>
       <c r="P372" s="7" t="inlineStr"/>
       <c r="Q372" s="6" t="inlineStr"/>
       <c r="R372" s="7" t="inlineStr">
@@ -31882,7 +31878,11 @@
       <c r="V372" s="7" t="inlineStr"/>
       <c r="W372" s="6" t="inlineStr"/>
       <c r="X372" s="7" t="inlineStr"/>
-      <c r="Y372" s="6" t="inlineStr"/>
+      <c r="Y372" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z372" s="7" t="inlineStr"/>
       <c r="AA372" s="6" t="inlineStr"/>
       <c r="AB372" s="6" t="inlineStr"/>
@@ -31950,11 +31950,7 @@
         </is>
       </c>
       <c r="N373" s="7" t="inlineStr"/>
-      <c r="O373" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O373" s="6" t="inlineStr"/>
       <c r="P373" s="7" t="inlineStr"/>
       <c r="Q373" s="6" t="inlineStr"/>
       <c r="R373" s="7" t="inlineStr">
@@ -31972,7 +31968,11 @@
       <c r="V373" s="7" t="inlineStr"/>
       <c r="W373" s="6" t="inlineStr"/>
       <c r="X373" s="7" t="inlineStr"/>
-      <c r="Y373" s="6" t="inlineStr"/>
+      <c r="Y373" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z373" s="7" t="inlineStr"/>
       <c r="AA373" s="6" t="inlineStr"/>
       <c r="AB373" s="6" t="inlineStr"/>
@@ -32040,11 +32040,7 @@
         </is>
       </c>
       <c r="N374" s="7" t="inlineStr"/>
-      <c r="O374" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O374" s="6" t="inlineStr"/>
       <c r="P374" s="7" t="inlineStr"/>
       <c r="Q374" s="6" t="inlineStr"/>
       <c r="R374" s="7" t="inlineStr">
@@ -32062,7 +32058,11 @@
       <c r="V374" s="7" t="inlineStr"/>
       <c r="W374" s="6" t="inlineStr"/>
       <c r="X374" s="7" t="inlineStr"/>
-      <c r="Y374" s="6" t="inlineStr"/>
+      <c r="Y374" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z374" s="7" t="inlineStr"/>
       <c r="AA374" s="6" t="inlineStr"/>
       <c r="AB374" s="6" t="inlineStr"/>
@@ -32130,11 +32130,7 @@
         </is>
       </c>
       <c r="N375" s="7" t="inlineStr"/>
-      <c r="O375" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O375" s="6" t="inlineStr"/>
       <c r="P375" s="7" t="inlineStr"/>
       <c r="Q375" s="6" t="inlineStr"/>
       <c r="R375" s="7" t="inlineStr">
@@ -32152,7 +32148,11 @@
       <c r="V375" s="7" t="inlineStr"/>
       <c r="W375" s="6" t="inlineStr"/>
       <c r="X375" s="7" t="inlineStr"/>
-      <c r="Y375" s="6" t="inlineStr"/>
+      <c r="Y375" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z375" s="7" t="inlineStr"/>
       <c r="AA375" s="6" t="inlineStr"/>
       <c r="AB375" s="6" t="inlineStr"/>
@@ -32220,11 +32220,7 @@
         </is>
       </c>
       <c r="N376" s="7" t="inlineStr"/>
-      <c r="O376" s="10" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O376" s="6" t="inlineStr"/>
       <c r="P376" s="7" t="inlineStr"/>
       <c r="Q376" s="6" t="inlineStr"/>
       <c r="R376" s="7" t="inlineStr">
@@ -32242,7 +32238,11 @@
       <c r="V376" s="7" t="inlineStr"/>
       <c r="W376" s="6" t="inlineStr"/>
       <c r="X376" s="7" t="inlineStr"/>
-      <c r="Y376" s="6" t="inlineStr"/>
+      <c r="Y376" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="Z376" s="7" t="inlineStr"/>
       <c r="AA376" s="6" t="inlineStr"/>
       <c r="AB376" s="6" t="inlineStr"/>
@@ -32672,7 +32672,11 @@
       <c r="N381" s="3" t="inlineStr"/>
       <c r="O381" s="2" t="inlineStr"/>
       <c r="P381" s="3" t="inlineStr"/>
-      <c r="Q381" s="2" t="inlineStr"/>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R381" s="3" t="inlineStr"/>
       <c r="S381" s="2" t="inlineStr"/>
       <c r="T381" s="3" t="inlineStr"/>
@@ -32685,11 +32689,7 @@
       </c>
       <c r="X381" s="3" t="inlineStr"/>
       <c r="Y381" s="2" t="inlineStr"/>
-      <c r="Z381" s="3" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="Z381" s="3" t="inlineStr"/>
       <c r="AA381" s="2" t="inlineStr"/>
       <c r="AB381" s="2" t="inlineStr"/>
       <c r="AC381" s="2" t="inlineStr">
@@ -32754,7 +32754,11 @@
       <c r="N382" s="7" t="inlineStr"/>
       <c r="O382" s="6" t="inlineStr"/>
       <c r="P382" s="7" t="inlineStr"/>
-      <c r="Q382" s="6" t="inlineStr"/>
+      <c r="Q382" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R382" s="7" t="inlineStr"/>
       <c r="S382" s="6" t="inlineStr"/>
       <c r="T382" s="7" t="inlineStr"/>
@@ -32767,11 +32771,7 @@
       </c>
       <c r="X382" s="7" t="inlineStr"/>
       <c r="Y382" s="6" t="inlineStr"/>
-      <c r="Z382" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="Z382" s="7" t="inlineStr"/>
       <c r="AA382" s="6" t="inlineStr"/>
       <c r="AB382" s="6" t="n">
         <v>0</v>
@@ -32838,7 +32838,11 @@
       <c r="N383" s="7" t="inlineStr"/>
       <c r="O383" s="6" t="inlineStr"/>
       <c r="P383" s="7" t="inlineStr"/>
-      <c r="Q383" s="6" t="inlineStr"/>
+      <c r="Q383" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R383" s="7" t="inlineStr"/>
       <c r="S383" s="6" t="inlineStr"/>
       <c r="T383" s="7" t="inlineStr"/>
@@ -32851,11 +32855,7 @@
       </c>
       <c r="X383" s="7" t="inlineStr"/>
       <c r="Y383" s="6" t="inlineStr"/>
-      <c r="Z383" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="Z383" s="7" t="inlineStr"/>
       <c r="AA383" s="6" t="inlineStr"/>
       <c r="AB383" s="6" t="n">
         <v>1</v>
@@ -32922,7 +32922,11 @@
       <c r="N384" s="7" t="inlineStr"/>
       <c r="O384" s="6" t="inlineStr"/>
       <c r="P384" s="7" t="inlineStr"/>
-      <c r="Q384" s="6" t="inlineStr"/>
+      <c r="Q384" s="6" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="R384" s="7" t="inlineStr"/>
       <c r="S384" s="6" t="inlineStr"/>
       <c r="T384" s="7" t="inlineStr"/>
@@ -32935,11 +32939,7 @@
       </c>
       <c r="X384" s="7" t="inlineStr"/>
       <c r="Y384" s="6" t="inlineStr"/>
-      <c r="Z384" s="7" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="Z384" s="7" t="inlineStr"/>
       <c r="AA384" s="6" t="inlineStr"/>
       <c r="AB384" s="6" t="n">
         <v>2</v>
@@ -33942,7 +33942,11 @@
       <c r="N397" s="3" t="inlineStr"/>
       <c r="O397" s="2" t="inlineStr"/>
       <c r="P397" s="3" t="inlineStr"/>
-      <c r="Q397" s="2" t="inlineStr"/>
+      <c r="Q397" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="R397" s="3" t="inlineStr">
         <is>
           <t>r</t>
@@ -33959,11 +33963,7 @@
       <c r="W397" s="2" t="inlineStr"/>
       <c r="X397" s="3" t="inlineStr"/>
       <c r="Y397" s="2" t="inlineStr"/>
-      <c r="Z397" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="Z397" s="3" t="inlineStr"/>
       <c r="AA397" s="2" t="inlineStr"/>
       <c r="AB397" s="2" t="inlineStr"/>
       <c r="AC397" s="2" t="inlineStr">
@@ -34035,14 +34035,14 @@
       <c r="U398" s="2" t="inlineStr"/>
       <c r="V398" s="3" t="inlineStr"/>
       <c r="W398" s="2" t="inlineStr"/>
-      <c r="X398" s="4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="X398" s="3" t="inlineStr"/>
       <c r="Y398" s="2" t="inlineStr"/>
       <c r="Z398" s="3" t="inlineStr"/>
-      <c r="AA398" s="2" t="inlineStr"/>
+      <c r="AA398" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="AB398" s="2" t="inlineStr"/>
       <c r="AC398" s="2" t="inlineStr">
         <is>
@@ -34105,7 +34105,11 @@
       </c>
       <c r="N399" s="3" t="inlineStr"/>
       <c r="O399" s="2" t="inlineStr"/>
-      <c r="P399" s="3" t="inlineStr"/>
+      <c r="P399" s="4" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q399" s="2" t="inlineStr"/>
       <c r="R399" s="3" t="inlineStr"/>
       <c r="S399" s="2" t="inlineStr"/>
@@ -34114,11 +34118,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U399" s="9" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U399" s="2" t="inlineStr"/>
       <c r="V399" s="3" t="inlineStr"/>
       <c r="W399" s="2" t="inlineStr"/>
       <c r="X399" s="3" t="inlineStr"/>
@@ -34187,7 +34187,11 @@
       </c>
       <c r="N400" s="3" t="inlineStr"/>
       <c r="O400" s="2" t="inlineStr"/>
-      <c r="P400" s="3" t="inlineStr"/>
+      <c r="P400" s="4" t="inlineStr">
+        <is>
+          <t>r/s</t>
+        </is>
+      </c>
       <c r="Q400" s="2" t="inlineStr"/>
       <c r="R400" s="3" t="inlineStr"/>
       <c r="S400" s="2" t="inlineStr"/>
@@ -34196,11 +34200,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="U400" s="9" t="inlineStr">
-        <is>
-          <t>r/s</t>
-        </is>
-      </c>
+      <c r="U400" s="2" t="inlineStr"/>
       <c r="V400" s="3" t="inlineStr"/>
       <c r="W400" s="2" t="inlineStr"/>
       <c r="X400" s="3" t="inlineStr"/>
